--- a/project/outputs_xlsx_solution/test33.4-wide-NF-1.xlsx
+++ b/project/outputs_xlsx_solution/test33.4-wide-NF-1.xlsx
@@ -936,18 +936,6 @@
       <c r="DR1">
         <v>119</v>
       </c>
-      <c r="DS1">
-        <v>120</v>
-      </c>
-      <c r="DT1">
-        <v>121</v>
-      </c>
-      <c r="DU1">
-        <v>122</v>
-      </c>
-      <c r="DV1">
-        <v>123</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2">
@@ -1426,12 +1414,9 @@
         <v>6</v>
       </c>
       <c r="W19" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="X19" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y19" t="s">
         <v>10</v>
       </c>
       <c r="AA19" t="s">
@@ -1455,7 +1440,7 @@
         <v>6</v>
       </c>
       <c r="X20" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="Y20" t="s">
         <v>26</v>
@@ -1577,12 +1562,9 @@
         <v>6</v>
       </c>
       <c r="AB24" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="AC24" t="s">
-        <v>8</v>
-      </c>
-      <c r="AD24" t="s">
         <v>10</v>
       </c>
       <c r="AH24" t="s">
@@ -1599,16 +1581,16 @@
       <c r="C25" t="s">
         <v>27</v>
       </c>
+      <c r="AC25" t="s">
+        <v>5</v>
+      </c>
       <c r="AD25" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE25" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AF25" t="s">
-        <v>8</v>
-      </c>
-      <c r="AG25" t="s">
         <v>10</v>
       </c>
       <c r="AH25" t="s">
@@ -1625,14 +1607,17 @@
       <c r="C26" t="s">
         <v>28</v>
       </c>
+      <c r="AD26" t="s">
+        <v>5</v>
+      </c>
       <c r="AE26" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF26" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AG26" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="AH26" t="s">
         <v>8</v>
@@ -1641,12 +1626,6 @@
         <v>8</v>
       </c>
       <c r="AJ26" t="s">
-        <v>8</v>
-      </c>
-      <c r="AK26" t="s">
-        <v>8</v>
-      </c>
-      <c r="AL26" t="s">
         <v>11</v>
       </c>
     </row>
@@ -1660,25 +1639,25 @@
       <c r="C27" t="s">
         <v>29</v>
       </c>
+      <c r="AE27" t="s">
+        <v>5</v>
+      </c>
       <c r="AF27" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG27" t="s">
-        <v>6</v>
-      </c>
-      <c r="AH27" t="s">
         <v>21</v>
       </c>
+      <c r="AJ27" t="s">
+        <v>8</v>
+      </c>
+      <c r="AK27" t="s">
+        <v>8</v>
+      </c>
       <c r="AL27" t="s">
         <v>8</v>
       </c>
       <c r="AM27" t="s">
-        <v>8</v>
-      </c>
-      <c r="AN27" t="s">
-        <v>8</v>
-      </c>
-      <c r="AO27" t="s">
         <v>11</v>
       </c>
     </row>
@@ -1692,19 +1671,19 @@
       <c r="C28" t="s">
         <v>30</v>
       </c>
+      <c r="AF28" t="s">
+        <v>5</v>
+      </c>
       <c r="AG28" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AH28" t="s">
-        <v>6</v>
-      </c>
-      <c r="AI28" t="s">
         <v>21</v>
       </c>
-      <c r="AO28" t="s">
-        <v>8</v>
-      </c>
-      <c r="AP28" t="s">
+      <c r="AM28" t="s">
+        <v>8</v>
+      </c>
+      <c r="AN28" t="s">
         <v>11</v>
       </c>
     </row>
@@ -1718,19 +1697,19 @@
       <c r="C29" t="s">
         <v>31</v>
       </c>
+      <c r="AG29" t="s">
+        <v>5</v>
+      </c>
       <c r="AH29" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AI29" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AJ29" t="s">
-        <v>8</v>
-      </c>
-      <c r="AK29" t="s">
-        <v>10</v>
-      </c>
-      <c r="AP29" t="s">
+        <v>10</v>
+      </c>
+      <c r="AN29" t="s">
         <v>11</v>
       </c>
     </row>
@@ -1744,22 +1723,19 @@
       <c r="C30" t="s">
         <v>32</v>
       </c>
+      <c r="AH30" t="s">
+        <v>5</v>
+      </c>
       <c r="AI30" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AJ30" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AK30" t="s">
-        <v>21</v>
-      </c>
-      <c r="AL30" t="s">
-        <v>8</v>
-      </c>
-      <c r="AM30" t="s">
-        <v>10</v>
-      </c>
-      <c r="AP30" t="s">
+        <v>10</v>
+      </c>
+      <c r="AN30" t="s">
         <v>11</v>
       </c>
     </row>
@@ -1773,19 +1749,19 @@
       <c r="C31" t="s">
         <v>27</v>
       </c>
+      <c r="AI31" t="s">
+        <v>5</v>
+      </c>
       <c r="AJ31" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AK31" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AL31" t="s">
-        <v>8</v>
-      </c>
-      <c r="AM31" t="s">
-        <v>10</v>
-      </c>
-      <c r="AP31" t="s">
+        <v>10</v>
+      </c>
+      <c r="AN31" t="s">
         <v>11</v>
       </c>
     </row>
@@ -1799,14 +1775,17 @@
       <c r="C32" t="s">
         <v>28</v>
       </c>
+      <c r="AJ32" t="s">
+        <v>5</v>
+      </c>
       <c r="AK32" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AL32" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AM32" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="AN32" t="s">
         <v>8</v>
@@ -1815,12 +1794,6 @@
         <v>8</v>
       </c>
       <c r="AP32" t="s">
-        <v>8</v>
-      </c>
-      <c r="AQ32" t="s">
-        <v>8</v>
-      </c>
-      <c r="AR32" t="s">
         <v>11</v>
       </c>
     </row>
@@ -1834,25 +1807,25 @@
       <c r="C33" t="s">
         <v>29</v>
       </c>
+      <c r="AK33" t="s">
+        <v>5</v>
+      </c>
       <c r="AL33" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AM33" t="s">
-        <v>6</v>
-      </c>
-      <c r="AN33" t="s">
         <v>21</v>
       </c>
+      <c r="AP33" t="s">
+        <v>8</v>
+      </c>
+      <c r="AQ33" t="s">
+        <v>8</v>
+      </c>
       <c r="AR33" t="s">
         <v>8</v>
       </c>
       <c r="AS33" t="s">
-        <v>8</v>
-      </c>
-      <c r="AT33" t="s">
-        <v>8</v>
-      </c>
-      <c r="AU33" t="s">
         <v>11</v>
       </c>
     </row>
@@ -1866,19 +1839,19 @@
       <c r="C34" t="s">
         <v>30</v>
       </c>
+      <c r="AL34" t="s">
+        <v>5</v>
+      </c>
       <c r="AM34" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AN34" t="s">
-        <v>6</v>
-      </c>
-      <c r="AO34" t="s">
         <v>21</v>
       </c>
-      <c r="AU34" t="s">
-        <v>8</v>
-      </c>
-      <c r="AV34" t="s">
+      <c r="AS34" t="s">
+        <v>8</v>
+      </c>
+      <c r="AT34" t="s">
         <v>11</v>
       </c>
     </row>
@@ -1892,19 +1865,19 @@
       <c r="C35" t="s">
         <v>31</v>
       </c>
+      <c r="AM35" t="s">
+        <v>5</v>
+      </c>
       <c r="AN35" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AO35" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AP35" t="s">
-        <v>8</v>
-      </c>
-      <c r="AQ35" t="s">
-        <v>10</v>
-      </c>
-      <c r="AV35" t="s">
+        <v>10</v>
+      </c>
+      <c r="AT35" t="s">
         <v>11</v>
       </c>
     </row>
@@ -1918,22 +1891,19 @@
       <c r="C36" t="s">
         <v>32</v>
       </c>
+      <c r="AN36" t="s">
+        <v>5</v>
+      </c>
       <c r="AO36" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AP36" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AQ36" t="s">
-        <v>21</v>
-      </c>
-      <c r="AR36" t="s">
-        <v>8</v>
-      </c>
-      <c r="AS36" t="s">
-        <v>10</v>
-      </c>
-      <c r="AV36" t="s">
+        <v>10</v>
+      </c>
+      <c r="AT36" t="s">
         <v>11</v>
       </c>
     </row>
@@ -1947,22 +1917,22 @@
       <c r="C37" t="s">
         <v>33</v>
       </c>
+      <c r="AQ37" t="s">
+        <v>5</v>
+      </c>
+      <c r="AR37" t="s">
+        <v>6</v>
+      </c>
       <c r="AS37" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AT37" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AU37" t="s">
         <v>8</v>
       </c>
       <c r="AV37" t="s">
-        <v>8</v>
-      </c>
-      <c r="AW37" t="s">
-        <v>8</v>
-      </c>
-      <c r="AX37" t="s">
         <v>11</v>
       </c>
     </row>
@@ -1976,25 +1946,25 @@
       <c r="C38" t="s">
         <v>34</v>
       </c>
+      <c r="AR38" t="s">
+        <v>5</v>
+      </c>
+      <c r="AS38" t="s">
+        <v>6</v>
+      </c>
       <c r="AT38" t="s">
-        <v>5</v>
-      </c>
-      <c r="AU38" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="AV38" t="s">
-        <v>21</v>
+        <v>8</v>
+      </c>
+      <c r="AW38" t="s">
+        <v>8</v>
       </c>
       <c r="AX38" t="s">
         <v>8</v>
       </c>
       <c r="AY38" t="s">
-        <v>8</v>
-      </c>
-      <c r="AZ38" t="s">
-        <v>8</v>
-      </c>
-      <c r="BA38" t="s">
         <v>11</v>
       </c>
     </row>
@@ -2008,19 +1978,19 @@
       <c r="C39" t="s">
         <v>35</v>
       </c>
+      <c r="AS39" t="s">
+        <v>5</v>
+      </c>
+      <c r="AT39" t="s">
+        <v>6</v>
+      </c>
       <c r="AU39" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AV39" t="s">
-        <v>6</v>
-      </c>
-      <c r="AW39" t="s">
-        <v>8</v>
-      </c>
-      <c r="AX39" t="s">
-        <v>10</v>
-      </c>
-      <c r="BA39" t="s">
+        <v>10</v>
+      </c>
+      <c r="AY39" t="s">
         <v>11</v>
       </c>
     </row>
@@ -2034,16 +2004,16 @@
       <c r="C40" t="s">
         <v>36</v>
       </c>
+      <c r="AT40" t="s">
+        <v>5</v>
+      </c>
       <c r="AV40" t="s">
-        <v>5</v>
-      </c>
-      <c r="AX40" t="s">
-        <v>8</v>
+        <v>8</v>
+      </c>
+      <c r="AW40" t="s">
+        <v>10</v>
       </c>
       <c r="AY40" t="s">
-        <v>10</v>
-      </c>
-      <c r="BA40" t="s">
         <v>11</v>
       </c>
     </row>
@@ -2057,22 +2027,22 @@
       <c r="C41" t="s">
         <v>18</v>
       </c>
+      <c r="AU41" t="s">
+        <v>5</v>
+      </c>
+      <c r="AV41" t="s">
+        <v>6</v>
+      </c>
       <c r="AW41" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AX41" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AY41" t="s">
         <v>8</v>
       </c>
       <c r="AZ41" t="s">
-        <v>8</v>
-      </c>
-      <c r="BA41" t="s">
-        <v>8</v>
-      </c>
-      <c r="BB41" t="s">
         <v>11</v>
       </c>
     </row>
@@ -2086,25 +2056,25 @@
       <c r="C42" t="s">
         <v>19</v>
       </c>
+      <c r="AV42" t="s">
+        <v>5</v>
+      </c>
+      <c r="AW42" t="s">
+        <v>6</v>
+      </c>
       <c r="AX42" t="s">
-        <v>5</v>
-      </c>
-      <c r="AY42" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="AZ42" t="s">
-        <v>21</v>
+        <v>8</v>
+      </c>
+      <c r="BA42" t="s">
+        <v>8</v>
       </c>
       <c r="BB42" t="s">
         <v>8</v>
       </c>
       <c r="BC42" t="s">
-        <v>8</v>
-      </c>
-      <c r="BD42" t="s">
-        <v>8</v>
-      </c>
-      <c r="BE42" t="s">
         <v>11</v>
       </c>
     </row>
@@ -2118,17 +2088,23 @@
       <c r="C43" t="s">
         <v>20</v>
       </c>
+      <c r="AW43" t="s">
+        <v>5</v>
+      </c>
+      <c r="AX43" t="s">
+        <v>6</v>
+      </c>
       <c r="AY43" t="s">
-        <v>5</v>
-      </c>
-      <c r="AZ43" t="s">
-        <v>6</v>
-      </c>
-      <c r="BA43" t="s">
         <v>21</v>
       </c>
+      <c r="BC43" t="s">
+        <v>26</v>
+      </c>
+      <c r="BD43" t="s">
+        <v>8</v>
+      </c>
       <c r="BE43" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="BF43" t="s">
         <v>8</v>
@@ -2137,12 +2113,6 @@
         <v>8</v>
       </c>
       <c r="BH43" t="s">
-        <v>8</v>
-      </c>
-      <c r="BI43" t="s">
-        <v>8</v>
-      </c>
-      <c r="BJ43" t="s">
         <v>11</v>
       </c>
     </row>
@@ -2156,11 +2126,17 @@
       <c r="C44" t="s">
         <v>22</v>
       </c>
+      <c r="AX44" t="s">
+        <v>5</v>
+      </c>
+      <c r="AY44" t="s">
+        <v>6</v>
+      </c>
       <c r="AZ44" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="BA44" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="BB44" t="s">
         <v>8</v>
@@ -2169,15 +2145,9 @@
         <v>8</v>
       </c>
       <c r="BD44" t="s">
-        <v>8</v>
-      </c>
-      <c r="BE44" t="s">
-        <v>8</v>
-      </c>
-      <c r="BF44" t="s">
-        <v>10</v>
-      </c>
-      <c r="BJ44" t="s">
+        <v>10</v>
+      </c>
+      <c r="BH44" t="s">
         <v>11</v>
       </c>
     </row>
@@ -2191,11 +2161,17 @@
       <c r="C45" t="s">
         <v>23</v>
       </c>
+      <c r="AY45" t="s">
+        <v>5</v>
+      </c>
+      <c r="AZ45" t="s">
+        <v>6</v>
+      </c>
       <c r="BA45" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="BB45" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="BC45" t="s">
         <v>8</v>
@@ -2210,15 +2186,9 @@
         <v>8</v>
       </c>
       <c r="BG45" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="BH45" t="s">
-        <v>8</v>
-      </c>
-      <c r="BI45" t="s">
-        <v>10</v>
-      </c>
-      <c r="BJ45" t="s">
         <v>11</v>
       </c>
     </row>
@@ -2232,19 +2202,19 @@
       <c r="C46" t="s">
         <v>24</v>
       </c>
+      <c r="AZ46" t="s">
+        <v>5</v>
+      </c>
+      <c r="BA46" t="s">
+        <v>6</v>
+      </c>
       <c r="BB46" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="BC46" t="s">
-        <v>6</v>
-      </c>
-      <c r="BD46" t="s">
-        <v>8</v>
-      </c>
-      <c r="BE46" t="s">
-        <v>10</v>
-      </c>
-      <c r="BJ46" t="s">
+        <v>10</v>
+      </c>
+      <c r="BH46" t="s">
         <v>11</v>
       </c>
     </row>
@@ -2258,19 +2228,19 @@
       <c r="C47" t="s">
         <v>16</v>
       </c>
+      <c r="BA47" t="s">
+        <v>5</v>
+      </c>
+      <c r="BB47" t="s">
+        <v>6</v>
+      </c>
       <c r="BC47" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="BD47" t="s">
-        <v>6</v>
-      </c>
-      <c r="BE47" t="s">
-        <v>8</v>
-      </c>
-      <c r="BF47" t="s">
-        <v>10</v>
-      </c>
-      <c r="BK47" t="s">
+        <v>10</v>
+      </c>
+      <c r="BI47" t="s">
         <v>11</v>
       </c>
     </row>
@@ -2284,19 +2254,19 @@
       <c r="C48" t="s">
         <v>25</v>
       </c>
+      <c r="BB48" t="s">
+        <v>5</v>
+      </c>
+      <c r="BC48" t="s">
+        <v>6</v>
+      </c>
       <c r="BD48" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="BE48" t="s">
-        <v>6</v>
-      </c>
-      <c r="BF48" t="s">
-        <v>8</v>
-      </c>
-      <c r="BG48" t="s">
-        <v>10</v>
-      </c>
-      <c r="BK48" t="s">
+        <v>10</v>
+      </c>
+      <c r="BI48" t="s">
         <v>11</v>
       </c>
     </row>
@@ -2310,22 +2280,19 @@
       <c r="C49" t="s">
         <v>27</v>
       </c>
+      <c r="BC49" t="s">
+        <v>5</v>
+      </c>
+      <c r="BD49" t="s">
+        <v>6</v>
+      </c>
       <c r="BE49" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="BF49" t="s">
-        <v>6</v>
-      </c>
-      <c r="BG49" t="s">
-        <v>21</v>
-      </c>
-      <c r="BH49" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="BI49" t="s">
-        <v>10</v>
-      </c>
-      <c r="BK49" t="s">
         <v>11</v>
       </c>
     </row>
@@ -2339,17 +2306,23 @@
       <c r="C50" t="s">
         <v>28</v>
       </c>
+      <c r="BD50" t="s">
+        <v>5</v>
+      </c>
+      <c r="BE50" t="s">
+        <v>6</v>
+      </c>
       <c r="BF50" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="BG50" t="s">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="BH50" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="BI50" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="BJ50" t="s">
         <v>8</v>
@@ -2358,12 +2331,6 @@
         <v>8</v>
       </c>
       <c r="BL50" t="s">
-        <v>8</v>
-      </c>
-      <c r="BM50" t="s">
-        <v>8</v>
-      </c>
-      <c r="BN50" t="s">
         <v>11</v>
       </c>
     </row>
@@ -2377,25 +2344,25 @@
       <c r="C51" t="s">
         <v>29</v>
       </c>
+      <c r="BE51" t="s">
+        <v>5</v>
+      </c>
+      <c r="BF51" t="s">
+        <v>6</v>
+      </c>
       <c r="BG51" t="s">
-        <v>5</v>
-      </c>
-      <c r="BH51" t="s">
-        <v>6</v>
-      </c>
-      <c r="BI51" t="s">
         <v>21</v>
       </c>
+      <c r="BL51" t="s">
+        <v>8</v>
+      </c>
+      <c r="BM51" t="s">
+        <v>8</v>
+      </c>
       <c r="BN51" t="s">
         <v>8</v>
       </c>
       <c r="BO51" t="s">
-        <v>8</v>
-      </c>
-      <c r="BP51" t="s">
-        <v>8</v>
-      </c>
-      <c r="BQ51" t="s">
         <v>11</v>
       </c>
     </row>
@@ -2409,19 +2376,19 @@
       <c r="C52" t="s">
         <v>30</v>
       </c>
+      <c r="BF52" t="s">
+        <v>5</v>
+      </c>
+      <c r="BG52" t="s">
+        <v>6</v>
+      </c>
       <c r="BH52" t="s">
-        <v>5</v>
-      </c>
-      <c r="BI52" t="s">
-        <v>6</v>
-      </c>
-      <c r="BJ52" t="s">
         <v>21</v>
       </c>
-      <c r="BQ52" t="s">
-        <v>8</v>
-      </c>
-      <c r="BR52" t="s">
+      <c r="BO52" t="s">
+        <v>8</v>
+      </c>
+      <c r="BP52" t="s">
         <v>11</v>
       </c>
     </row>
@@ -2435,19 +2402,19 @@
       <c r="C53" t="s">
         <v>31</v>
       </c>
+      <c r="BG53" t="s">
+        <v>5</v>
+      </c>
+      <c r="BH53" t="s">
+        <v>6</v>
+      </c>
       <c r="BI53" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="BJ53" t="s">
-        <v>6</v>
-      </c>
-      <c r="BK53" t="s">
-        <v>8</v>
-      </c>
-      <c r="BL53" t="s">
-        <v>10</v>
-      </c>
-      <c r="BR53" t="s">
+        <v>10</v>
+      </c>
+      <c r="BP53" t="s">
         <v>11</v>
       </c>
     </row>
@@ -2461,22 +2428,19 @@
       <c r="C54" t="s">
         <v>32</v>
       </c>
+      <c r="BH54" t="s">
+        <v>5</v>
+      </c>
+      <c r="BI54" t="s">
+        <v>6</v>
+      </c>
       <c r="BJ54" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="BK54" t="s">
-        <v>6</v>
-      </c>
-      <c r="BL54" t="s">
-        <v>21</v>
-      </c>
-      <c r="BM54" t="s">
-        <v>8</v>
-      </c>
-      <c r="BN54" t="s">
-        <v>10</v>
-      </c>
-      <c r="BR54" t="s">
+        <v>10</v>
+      </c>
+      <c r="BP54" t="s">
         <v>11</v>
       </c>
     </row>
@@ -2490,19 +2454,19 @@
       <c r="C55" t="s">
         <v>27</v>
       </c>
+      <c r="BI55" t="s">
+        <v>5</v>
+      </c>
+      <c r="BJ55" t="s">
+        <v>6</v>
+      </c>
       <c r="BK55" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="BL55" t="s">
-        <v>6</v>
-      </c>
-      <c r="BM55" t="s">
-        <v>8</v>
-      </c>
-      <c r="BN55" t="s">
-        <v>10</v>
-      </c>
-      <c r="BR55" t="s">
+        <v>10</v>
+      </c>
+      <c r="BP55" t="s">
         <v>11</v>
       </c>
     </row>
@@ -2516,28 +2480,28 @@
       <c r="C56" t="s">
         <v>28</v>
       </c>
+      <c r="BJ56" t="s">
+        <v>5</v>
+      </c>
+      <c r="BK56" t="s">
+        <v>6</v>
+      </c>
       <c r="BL56" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="BM56" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="BN56" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="BO56" t="s">
         <v>8</v>
       </c>
       <c r="BP56" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="BQ56" t="s">
-        <v>8</v>
-      </c>
-      <c r="BR56" t="s">
-        <v>8</v>
-      </c>
-      <c r="BS56" t="s">
         <v>11</v>
       </c>
     </row>
@@ -2551,25 +2515,25 @@
       <c r="C57" t="s">
         <v>29</v>
       </c>
+      <c r="BK57" t="s">
+        <v>5</v>
+      </c>
+      <c r="BL57" t="s">
+        <v>6</v>
+      </c>
       <c r="BM57" t="s">
-        <v>5</v>
-      </c>
-      <c r="BN57" t="s">
-        <v>6</v>
-      </c>
-      <c r="BO57" t="s">
         <v>21</v>
       </c>
+      <c r="BP57" t="s">
+        <v>8</v>
+      </c>
+      <c r="BQ57" t="s">
+        <v>8</v>
+      </c>
+      <c r="BR57" t="s">
+        <v>8</v>
+      </c>
       <c r="BS57" t="s">
-        <v>8</v>
-      </c>
-      <c r="BT57" t="s">
-        <v>8</v>
-      </c>
-      <c r="BU57" t="s">
-        <v>8</v>
-      </c>
-      <c r="BV57" t="s">
         <v>11</v>
       </c>
     </row>
@@ -2583,19 +2547,19 @@
       <c r="C58" t="s">
         <v>30</v>
       </c>
+      <c r="BL58" t="s">
+        <v>5</v>
+      </c>
+      <c r="BM58" t="s">
+        <v>6</v>
+      </c>
       <c r="BN58" t="s">
-        <v>5</v>
-      </c>
-      <c r="BO58" t="s">
-        <v>6</v>
-      </c>
-      <c r="BP58" t="s">
         <v>21</v>
       </c>
-      <c r="BV58" t="s">
-        <v>8</v>
-      </c>
-      <c r="BW58" t="s">
+      <c r="BS58" t="s">
+        <v>8</v>
+      </c>
+      <c r="BT58" t="s">
         <v>11</v>
       </c>
     </row>
@@ -2609,22 +2573,19 @@
       <c r="C59" t="s">
         <v>31</v>
       </c>
+      <c r="BM59" t="s">
+        <v>5</v>
+      </c>
+      <c r="BN59" t="s">
+        <v>6</v>
+      </c>
       <c r="BO59" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="BP59" t="s">
-        <v>6</v>
-      </c>
-      <c r="BQ59" t="s">
-        <v>21</v>
-      </c>
-      <c r="BR59" t="s">
-        <v>8</v>
-      </c>
-      <c r="BS59" t="s">
-        <v>10</v>
-      </c>
-      <c r="BW59" t="s">
+        <v>10</v>
+      </c>
+      <c r="BT59" t="s">
         <v>11</v>
       </c>
     </row>
@@ -2638,22 +2599,19 @@
       <c r="C60" t="s">
         <v>32</v>
       </c>
+      <c r="BN60" t="s">
+        <v>5</v>
+      </c>
+      <c r="BO60" t="s">
+        <v>6</v>
+      </c>
       <c r="BP60" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="BQ60" t="s">
-        <v>6</v>
-      </c>
-      <c r="BR60" t="s">
-        <v>21</v>
-      </c>
-      <c r="BS60" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="BT60" t="s">
-        <v>10</v>
-      </c>
-      <c r="BW60" t="s">
         <v>11</v>
       </c>
     </row>
@@ -2667,19 +2625,19 @@
       <c r="C61" t="s">
         <v>27</v>
       </c>
+      <c r="BO61" t="s">
+        <v>5</v>
+      </c>
+      <c r="BP61" t="s">
+        <v>6</v>
+      </c>
       <c r="BQ61" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="BR61" t="s">
-        <v>6</v>
-      </c>
-      <c r="BS61" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="BT61" t="s">
-        <v>10</v>
-      </c>
-      <c r="BW61" t="s">
         <v>11</v>
       </c>
     </row>
@@ -2693,28 +2651,25 @@
       <c r="C62" t="s">
         <v>28</v>
       </c>
+      <c r="BP62" t="s">
+        <v>5</v>
+      </c>
+      <c r="BQ62" t="s">
+        <v>6</v>
+      </c>
       <c r="BR62" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="BS62" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="BT62" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="BU62" t="s">
         <v>8</v>
       </c>
       <c r="BV62" t="s">
-        <v>8</v>
-      </c>
-      <c r="BW62" t="s">
-        <v>8</v>
-      </c>
-      <c r="BX62" t="s">
-        <v>8</v>
-      </c>
-      <c r="BY62" t="s">
         <v>11</v>
       </c>
     </row>
@@ -2728,25 +2683,25 @@
       <c r="C63" t="s">
         <v>29</v>
       </c>
+      <c r="BQ63" t="s">
+        <v>5</v>
+      </c>
+      <c r="BR63" t="s">
+        <v>6</v>
+      </c>
       <c r="BS63" t="s">
-        <v>5</v>
-      </c>
-      <c r="BT63" t="s">
-        <v>6</v>
-      </c>
-      <c r="BU63" t="s">
         <v>21</v>
       </c>
+      <c r="BV63" t="s">
+        <v>8</v>
+      </c>
+      <c r="BW63" t="s">
+        <v>8</v>
+      </c>
+      <c r="BX63" t="s">
+        <v>8</v>
+      </c>
       <c r="BY63" t="s">
-        <v>8</v>
-      </c>
-      <c r="BZ63" t="s">
-        <v>8</v>
-      </c>
-      <c r="CA63" t="s">
-        <v>8</v>
-      </c>
-      <c r="CB63" t="s">
         <v>11</v>
       </c>
     </row>
@@ -2760,19 +2715,19 @@
       <c r="C64" t="s">
         <v>30</v>
       </c>
+      <c r="BR64" t="s">
+        <v>5</v>
+      </c>
+      <c r="BS64" t="s">
+        <v>6</v>
+      </c>
       <c r="BT64" t="s">
-        <v>5</v>
-      </c>
-      <c r="BU64" t="s">
-        <v>6</v>
-      </c>
-      <c r="BV64" t="s">
         <v>21</v>
       </c>
-      <c r="CB64" t="s">
-        <v>8</v>
-      </c>
-      <c r="CC64" t="s">
+      <c r="BY64" t="s">
+        <v>8</v>
+      </c>
+      <c r="BZ64" t="s">
         <v>11</v>
       </c>
     </row>
@@ -2786,19 +2741,19 @@
       <c r="C65" t="s">
         <v>31</v>
       </c>
+      <c r="BS65" t="s">
+        <v>5</v>
+      </c>
+      <c r="BT65" t="s">
+        <v>6</v>
+      </c>
       <c r="BU65" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="BV65" t="s">
-        <v>6</v>
-      </c>
-      <c r="BW65" t="s">
-        <v>8</v>
-      </c>
-      <c r="BX65" t="s">
-        <v>10</v>
-      </c>
-      <c r="CC65" t="s">
+        <v>10</v>
+      </c>
+      <c r="BZ65" t="s">
         <v>11</v>
       </c>
     </row>
@@ -2812,22 +2767,19 @@
       <c r="C66" t="s">
         <v>32</v>
       </c>
+      <c r="BT66" t="s">
+        <v>5</v>
+      </c>
+      <c r="BU66" t="s">
+        <v>6</v>
+      </c>
       <c r="BV66" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="BW66" t="s">
-        <v>6</v>
-      </c>
-      <c r="BX66" t="s">
-        <v>21</v>
-      </c>
-      <c r="BY66" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="BZ66" t="s">
-        <v>10</v>
-      </c>
-      <c r="CC66" t="s">
         <v>11</v>
       </c>
     </row>
@@ -2841,22 +2793,22 @@
       <c r="C67" t="s">
         <v>33</v>
       </c>
+      <c r="BW67" t="s">
+        <v>5</v>
+      </c>
+      <c r="BX67" t="s">
+        <v>6</v>
+      </c>
+      <c r="BY67" t="s">
+        <v>8</v>
+      </c>
       <c r="BZ67" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="CA67" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="CB67" t="s">
-        <v>8</v>
-      </c>
-      <c r="CC67" t="s">
-        <v>8</v>
-      </c>
-      <c r="CD67" t="s">
-        <v>8</v>
-      </c>
-      <c r="CE67" t="s">
         <v>11</v>
       </c>
     </row>
@@ -2870,25 +2822,25 @@
       <c r="C68" t="s">
         <v>34</v>
       </c>
-      <c r="CA68" t="s">
-        <v>5</v>
+      <c r="BX68" t="s">
+        <v>5</v>
+      </c>
+      <c r="BY68" t="s">
+        <v>6</v>
+      </c>
+      <c r="BZ68" t="s">
+        <v>21</v>
       </c>
       <c r="CB68" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="CC68" t="s">
-        <v>21</v>
+        <v>8</v>
+      </c>
+      <c r="CD68" t="s">
+        <v>8</v>
       </c>
       <c r="CE68" t="s">
-        <v>8</v>
-      </c>
-      <c r="CF68" t="s">
-        <v>8</v>
-      </c>
-      <c r="CG68" t="s">
-        <v>8</v>
-      </c>
-      <c r="CH68" t="s">
         <v>11</v>
       </c>
     </row>
@@ -2902,19 +2854,19 @@
       <c r="C69" t="s">
         <v>35</v>
       </c>
+      <c r="BY69" t="s">
+        <v>5</v>
+      </c>
+      <c r="BZ69" t="s">
+        <v>6</v>
+      </c>
+      <c r="CA69" t="s">
+        <v>8</v>
+      </c>
       <c r="CB69" t="s">
-        <v>5</v>
-      </c>
-      <c r="CC69" t="s">
-        <v>6</v>
-      </c>
-      <c r="CD69" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="CE69" t="s">
-        <v>10</v>
-      </c>
-      <c r="CH69" t="s">
         <v>11</v>
       </c>
     </row>
@@ -2928,19 +2880,19 @@
       <c r="C70" t="s">
         <v>36</v>
       </c>
+      <c r="BZ70" t="s">
+        <v>5</v>
+      </c>
+      <c r="CA70" t="s">
+        <v>6</v>
+      </c>
+      <c r="CB70" t="s">
+        <v>8</v>
+      </c>
       <c r="CC70" t="s">
-        <v>5</v>
-      </c>
-      <c r="CD70" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="CE70" t="s">
-        <v>8</v>
-      </c>
-      <c r="CF70" t="s">
-        <v>10</v>
-      </c>
-      <c r="CH70" t="s">
         <v>11</v>
       </c>
     </row>
@@ -2954,22 +2906,22 @@
       <c r="C71" t="s">
         <v>18</v>
       </c>
+      <c r="CA71" t="s">
+        <v>5</v>
+      </c>
+      <c r="CB71" t="s">
+        <v>6</v>
+      </c>
+      <c r="CC71" t="s">
+        <v>8</v>
+      </c>
       <c r="CD71" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="CE71" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="CF71" t="s">
-        <v>8</v>
-      </c>
-      <c r="CG71" t="s">
-        <v>8</v>
-      </c>
-      <c r="CH71" t="s">
-        <v>8</v>
-      </c>
-      <c r="CI71" t="s">
         <v>11</v>
       </c>
     </row>
@@ -2983,25 +2935,25 @@
       <c r="C72" t="s">
         <v>19</v>
       </c>
-      <c r="CE72" t="s">
-        <v>5</v>
+      <c r="CB72" t="s">
+        <v>5</v>
+      </c>
+      <c r="CC72" t="s">
+        <v>6</v>
+      </c>
+      <c r="CD72" t="s">
+        <v>21</v>
       </c>
       <c r="CF72" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="CG72" t="s">
-        <v>21</v>
+        <v>8</v>
+      </c>
+      <c r="CH72" t="s">
+        <v>8</v>
       </c>
       <c r="CI72" t="s">
-        <v>8</v>
-      </c>
-      <c r="CJ72" t="s">
-        <v>8</v>
-      </c>
-      <c r="CK72" t="s">
-        <v>8</v>
-      </c>
-      <c r="CL72" t="s">
         <v>11</v>
       </c>
     </row>
@@ -3015,31 +2967,31 @@
       <c r="C73" t="s">
         <v>20</v>
       </c>
-      <c r="CF73" t="s">
-        <v>5</v>
-      </c>
-      <c r="CG73" t="s">
-        <v>6</v>
-      </c>
-      <c r="CH73" t="s">
+      <c r="CC73" t="s">
+        <v>5</v>
+      </c>
+      <c r="CD73" t="s">
+        <v>6</v>
+      </c>
+      <c r="CE73" t="s">
         <v>21</v>
       </c>
+      <c r="CI73" t="s">
+        <v>26</v>
+      </c>
+      <c r="CJ73" t="s">
+        <v>8</v>
+      </c>
+      <c r="CK73" t="s">
+        <v>8</v>
+      </c>
       <c r="CL73" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="CM73" t="s">
         <v>8</v>
       </c>
       <c r="CN73" t="s">
-        <v>8</v>
-      </c>
-      <c r="CO73" t="s">
-        <v>8</v>
-      </c>
-      <c r="CP73" t="s">
-        <v>8</v>
-      </c>
-      <c r="CQ73" t="s">
         <v>11</v>
       </c>
     </row>
@@ -3053,28 +3005,28 @@
       <c r="C74" t="s">
         <v>22</v>
       </c>
+      <c r="CD74" t="s">
+        <v>5</v>
+      </c>
+      <c r="CE74" t="s">
+        <v>6</v>
+      </c>
+      <c r="CF74" t="s">
+        <v>8</v>
+      </c>
       <c r="CG74" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="CH74" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="CI74" t="s">
         <v>8</v>
       </c>
       <c r="CJ74" t="s">
-        <v>8</v>
-      </c>
-      <c r="CK74" t="s">
-        <v>8</v>
-      </c>
-      <c r="CL74" t="s">
-        <v>8</v>
-      </c>
-      <c r="CM74" t="s">
-        <v>10</v>
-      </c>
-      <c r="CQ74" t="s">
+        <v>10</v>
+      </c>
+      <c r="CN74" t="s">
         <v>11</v>
       </c>
     </row>
@@ -3088,11 +3040,20 @@
       <c r="C75" t="s">
         <v>23</v>
       </c>
+      <c r="CE75" t="s">
+        <v>5</v>
+      </c>
+      <c r="CF75" t="s">
+        <v>6</v>
+      </c>
+      <c r="CG75" t="s">
+        <v>8</v>
+      </c>
       <c r="CH75" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="CI75" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="CJ75" t="s">
         <v>8</v>
@@ -3104,18 +3065,9 @@
         <v>8</v>
       </c>
       <c r="CM75" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="CN75" t="s">
-        <v>8</v>
-      </c>
-      <c r="CO75" t="s">
-        <v>8</v>
-      </c>
-      <c r="CP75" t="s">
-        <v>10</v>
-      </c>
-      <c r="CQ75" t="s">
         <v>11</v>
       </c>
     </row>
@@ -3129,19 +3081,19 @@
       <c r="C76" t="s">
         <v>24</v>
       </c>
+      <c r="CF76" t="s">
+        <v>5</v>
+      </c>
+      <c r="CG76" t="s">
+        <v>6</v>
+      </c>
+      <c r="CH76" t="s">
+        <v>8</v>
+      </c>
       <c r="CI76" t="s">
-        <v>5</v>
-      </c>
-      <c r="CJ76" t="s">
-        <v>6</v>
-      </c>
-      <c r="CK76" t="s">
-        <v>8</v>
-      </c>
-      <c r="CL76" t="s">
-        <v>10</v>
-      </c>
-      <c r="CQ76" t="s">
+        <v>10</v>
+      </c>
+      <c r="CN76" t="s">
         <v>11</v>
       </c>
     </row>
@@ -3155,19 +3107,19 @@
       <c r="C77" t="s">
         <v>16</v>
       </c>
+      <c r="CG77" t="s">
+        <v>5</v>
+      </c>
+      <c r="CH77" t="s">
+        <v>6</v>
+      </c>
+      <c r="CI77" t="s">
+        <v>8</v>
+      </c>
       <c r="CJ77" t="s">
-        <v>5</v>
-      </c>
-      <c r="CK77" t="s">
-        <v>6</v>
-      </c>
-      <c r="CL77" t="s">
-        <v>8</v>
-      </c>
-      <c r="CM77" t="s">
-        <v>10</v>
-      </c>
-      <c r="CR77" t="s">
+        <v>10</v>
+      </c>
+      <c r="CO77" t="s">
         <v>11</v>
       </c>
     </row>
@@ -3181,19 +3133,19 @@
       <c r="C78" t="s">
         <v>25</v>
       </c>
+      <c r="CH78" t="s">
+        <v>5</v>
+      </c>
+      <c r="CI78" t="s">
+        <v>6</v>
+      </c>
+      <c r="CJ78" t="s">
+        <v>8</v>
+      </c>
       <c r="CK78" t="s">
-        <v>5</v>
-      </c>
-      <c r="CL78" t="s">
-        <v>6</v>
-      </c>
-      <c r="CM78" t="s">
-        <v>8</v>
-      </c>
-      <c r="CN78" t="s">
-        <v>10</v>
-      </c>
-      <c r="CR78" t="s">
+        <v>10</v>
+      </c>
+      <c r="CO78" t="s">
         <v>11</v>
       </c>
     </row>
@@ -3207,22 +3159,19 @@
       <c r="C79" t="s">
         <v>27</v>
       </c>
+      <c r="CI79" t="s">
+        <v>5</v>
+      </c>
+      <c r="CJ79" t="s">
+        <v>6</v>
+      </c>
+      <c r="CK79" t="s">
+        <v>8</v>
+      </c>
       <c r="CL79" t="s">
-        <v>5</v>
-      </c>
-      <c r="CM79" t="s">
-        <v>6</v>
-      </c>
-      <c r="CN79" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="CO79" t="s">
-        <v>8</v>
-      </c>
-      <c r="CP79" t="s">
-        <v>10</v>
-      </c>
-      <c r="CR79" t="s">
         <v>11</v>
       </c>
     </row>
@@ -3236,31 +3185,31 @@
       <c r="C80" t="s">
         <v>28</v>
       </c>
+      <c r="CJ80" t="s">
+        <v>5</v>
+      </c>
+      <c r="CK80" t="s">
+        <v>6</v>
+      </c>
+      <c r="CL80" t="s">
+        <v>26</v>
+      </c>
       <c r="CM80" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="CN80" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="CO80" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="CP80" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="CQ80" t="s">
         <v>8</v>
       </c>
       <c r="CR80" t="s">
-        <v>8</v>
-      </c>
-      <c r="CS80" t="s">
-        <v>8</v>
-      </c>
-      <c r="CT80" t="s">
-        <v>8</v>
-      </c>
-      <c r="CU80" t="s">
         <v>11</v>
       </c>
     </row>
@@ -3274,25 +3223,25 @@
       <c r="C81" t="s">
         <v>29</v>
       </c>
-      <c r="CN81" t="s">
-        <v>5</v>
-      </c>
-      <c r="CO81" t="s">
-        <v>6</v>
-      </c>
-      <c r="CP81" t="s">
+      <c r="CK81" t="s">
+        <v>5</v>
+      </c>
+      <c r="CL81" t="s">
+        <v>6</v>
+      </c>
+      <c r="CM81" t="s">
         <v>21</v>
       </c>
+      <c r="CR81" t="s">
+        <v>8</v>
+      </c>
+      <c r="CS81" t="s">
+        <v>8</v>
+      </c>
+      <c r="CT81" t="s">
+        <v>8</v>
+      </c>
       <c r="CU81" t="s">
-        <v>8</v>
-      </c>
-      <c r="CV81" t="s">
-        <v>8</v>
-      </c>
-      <c r="CW81" t="s">
-        <v>8</v>
-      </c>
-      <c r="CX81" t="s">
         <v>11</v>
       </c>
     </row>
@@ -3306,19 +3255,19 @@
       <c r="C82" t="s">
         <v>30</v>
       </c>
-      <c r="CO82" t="s">
-        <v>5</v>
-      </c>
-      <c r="CP82" t="s">
-        <v>6</v>
-      </c>
-      <c r="CQ82" t="s">
+      <c r="CL82" t="s">
+        <v>5</v>
+      </c>
+      <c r="CM82" t="s">
+        <v>6</v>
+      </c>
+      <c r="CN82" t="s">
         <v>21</v>
       </c>
-      <c r="CX82" t="s">
-        <v>8</v>
-      </c>
-      <c r="CY82" t="s">
+      <c r="CU82" t="s">
+        <v>8</v>
+      </c>
+      <c r="CV82" t="s">
         <v>11</v>
       </c>
     </row>
@@ -3332,19 +3281,19 @@
       <c r="C83" t="s">
         <v>31</v>
       </c>
+      <c r="CM83" t="s">
+        <v>5</v>
+      </c>
+      <c r="CN83" t="s">
+        <v>6</v>
+      </c>
+      <c r="CO83" t="s">
+        <v>8</v>
+      </c>
       <c r="CP83" t="s">
-        <v>5</v>
-      </c>
-      <c r="CQ83" t="s">
-        <v>6</v>
-      </c>
-      <c r="CR83" t="s">
-        <v>8</v>
-      </c>
-      <c r="CS83" t="s">
-        <v>10</v>
-      </c>
-      <c r="CY83" t="s">
+        <v>10</v>
+      </c>
+      <c r="CV83" t="s">
         <v>11</v>
       </c>
     </row>
@@ -3358,22 +3307,19 @@
       <c r="C84" t="s">
         <v>32</v>
       </c>
+      <c r="CN84" t="s">
+        <v>5</v>
+      </c>
+      <c r="CO84" t="s">
+        <v>6</v>
+      </c>
+      <c r="CP84" t="s">
+        <v>8</v>
+      </c>
       <c r="CQ84" t="s">
-        <v>5</v>
-      </c>
-      <c r="CR84" t="s">
-        <v>6</v>
-      </c>
-      <c r="CS84" t="s">
-        <v>21</v>
-      </c>
-      <c r="CT84" t="s">
-        <v>8</v>
-      </c>
-      <c r="CU84" t="s">
-        <v>10</v>
-      </c>
-      <c r="CY84" t="s">
+        <v>10</v>
+      </c>
+      <c r="CV84" t="s">
         <v>11</v>
       </c>
     </row>
@@ -3387,19 +3333,19 @@
       <c r="C85" t="s">
         <v>27</v>
       </c>
+      <c r="CO85" t="s">
+        <v>5</v>
+      </c>
+      <c r="CP85" t="s">
+        <v>6</v>
+      </c>
+      <c r="CQ85" t="s">
+        <v>8</v>
+      </c>
       <c r="CR85" t="s">
-        <v>5</v>
-      </c>
-      <c r="CS85" t="s">
-        <v>6</v>
-      </c>
-      <c r="CT85" t="s">
-        <v>8</v>
-      </c>
-      <c r="CU85" t="s">
-        <v>10</v>
-      </c>
-      <c r="CY85" t="s">
+        <v>10</v>
+      </c>
+      <c r="CV85" t="s">
         <v>11</v>
       </c>
     </row>
@@ -3413,28 +3359,28 @@
       <c r="C86" t="s">
         <v>28</v>
       </c>
+      <c r="CP86" t="s">
+        <v>5</v>
+      </c>
+      <c r="CQ86" t="s">
+        <v>6</v>
+      </c>
+      <c r="CR86" t="s">
+        <v>8</v>
+      </c>
       <c r="CS86" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="CT86" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="CU86" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="CV86" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="CW86" t="s">
-        <v>8</v>
-      </c>
-      <c r="CX86" t="s">
-        <v>8</v>
-      </c>
-      <c r="CY86" t="s">
-        <v>8</v>
-      </c>
-      <c r="CZ86" t="s">
         <v>11</v>
       </c>
     </row>
@@ -3448,25 +3394,25 @@
       <c r="C87" t="s">
         <v>29</v>
       </c>
-      <c r="CT87" t="s">
-        <v>5</v>
-      </c>
-      <c r="CU87" t="s">
-        <v>6</v>
+      <c r="CQ87" t="s">
+        <v>5</v>
+      </c>
+      <c r="CR87" t="s">
+        <v>6</v>
+      </c>
+      <c r="CS87" t="s">
+        <v>21</v>
       </c>
       <c r="CV87" t="s">
-        <v>21</v>
-      </c>
-      <c r="CZ87" t="s">
-        <v>8</v>
-      </c>
-      <c r="DA87" t="s">
-        <v>8</v>
-      </c>
-      <c r="DB87" t="s">
-        <v>8</v>
-      </c>
-      <c r="DC87" t="s">
+        <v>8</v>
+      </c>
+      <c r="CW87" t="s">
+        <v>8</v>
+      </c>
+      <c r="CX87" t="s">
+        <v>8</v>
+      </c>
+      <c r="CY87" t="s">
         <v>11</v>
       </c>
     </row>
@@ -3480,19 +3426,19 @@
       <c r="C88" t="s">
         <v>30</v>
       </c>
-      <c r="CU88" t="s">
-        <v>5</v>
-      </c>
-      <c r="CV88" t="s">
-        <v>6</v>
-      </c>
-      <c r="CW88" t="s">
+      <c r="CR88" t="s">
+        <v>5</v>
+      </c>
+      <c r="CS88" t="s">
+        <v>6</v>
+      </c>
+      <c r="CT88" t="s">
         <v>21</v>
       </c>
-      <c r="DC88" t="s">
-        <v>8</v>
-      </c>
-      <c r="DD88" t="s">
+      <c r="CY88" t="s">
+        <v>8</v>
+      </c>
+      <c r="CZ88" t="s">
         <v>11</v>
       </c>
     </row>
@@ -3506,22 +3452,19 @@
       <c r="C89" t="s">
         <v>31</v>
       </c>
+      <c r="CS89" t="s">
+        <v>5</v>
+      </c>
+      <c r="CT89" t="s">
+        <v>6</v>
+      </c>
+      <c r="CU89" t="s">
+        <v>8</v>
+      </c>
       <c r="CV89" t="s">
-        <v>5</v>
-      </c>
-      <c r="CW89" t="s">
-        <v>6</v>
-      </c>
-      <c r="CX89" t="s">
-        <v>21</v>
-      </c>
-      <c r="CY89" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="CZ89" t="s">
-        <v>10</v>
-      </c>
-      <c r="DD89" t="s">
         <v>11</v>
       </c>
     </row>
@@ -3535,22 +3478,19 @@
       <c r="C90" t="s">
         <v>32</v>
       </c>
+      <c r="CT90" t="s">
+        <v>5</v>
+      </c>
+      <c r="CU90" t="s">
+        <v>6</v>
+      </c>
+      <c r="CV90" t="s">
+        <v>8</v>
+      </c>
       <c r="CW90" t="s">
-        <v>5</v>
-      </c>
-      <c r="CX90" t="s">
-        <v>6</v>
-      </c>
-      <c r="CY90" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="CZ90" t="s">
-        <v>8</v>
-      </c>
-      <c r="DA90" t="s">
-        <v>10</v>
-      </c>
-      <c r="DD90" t="s">
         <v>11</v>
       </c>
     </row>
@@ -3564,19 +3504,19 @@
       <c r="C91" t="s">
         <v>27</v>
       </c>
+      <c r="CU91" t="s">
+        <v>5</v>
+      </c>
+      <c r="CV91" t="s">
+        <v>6</v>
+      </c>
+      <c r="CW91" t="s">
+        <v>8</v>
+      </c>
       <c r="CX91" t="s">
-        <v>5</v>
-      </c>
-      <c r="CY91" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="CZ91" t="s">
-        <v>8</v>
-      </c>
-      <c r="DA91" t="s">
-        <v>10</v>
-      </c>
-      <c r="DD91" t="s">
         <v>11</v>
       </c>
     </row>
@@ -3590,28 +3530,25 @@
       <c r="C92" t="s">
         <v>28</v>
       </c>
+      <c r="CV92" t="s">
+        <v>5</v>
+      </c>
+      <c r="CW92" t="s">
+        <v>6</v>
+      </c>
+      <c r="CX92" t="s">
+        <v>8</v>
+      </c>
       <c r="CY92" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="CZ92" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="DA92" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="DB92" t="s">
-        <v>8</v>
-      </c>
-      <c r="DC92" t="s">
-        <v>8</v>
-      </c>
-      <c r="DD92" t="s">
-        <v>8</v>
-      </c>
-      <c r="DE92" t="s">
-        <v>8</v>
-      </c>
-      <c r="DF92" t="s">
         <v>11</v>
       </c>
     </row>
@@ -3625,25 +3562,25 @@
       <c r="C93" t="s">
         <v>29</v>
       </c>
-      <c r="CZ93" t="s">
-        <v>5</v>
-      </c>
-      <c r="DA93" t="s">
-        <v>6</v>
+      <c r="CW93" t="s">
+        <v>5</v>
+      </c>
+      <c r="CX93" t="s">
+        <v>6</v>
+      </c>
+      <c r="CY93" t="s">
+        <v>21</v>
       </c>
       <c r="DB93" t="s">
-        <v>21</v>
-      </c>
-      <c r="DF93" t="s">
-        <v>8</v>
-      </c>
-      <c r="DG93" t="s">
-        <v>8</v>
-      </c>
-      <c r="DH93" t="s">
-        <v>8</v>
-      </c>
-      <c r="DI93" t="s">
+        <v>8</v>
+      </c>
+      <c r="DC93" t="s">
+        <v>8</v>
+      </c>
+      <c r="DD93" t="s">
+        <v>8</v>
+      </c>
+      <c r="DE93" t="s">
         <v>11</v>
       </c>
     </row>
@@ -3657,19 +3594,19 @@
       <c r="C94" t="s">
         <v>30</v>
       </c>
-      <c r="DA94" t="s">
-        <v>5</v>
-      </c>
-      <c r="DB94" t="s">
-        <v>6</v>
-      </c>
-      <c r="DC94" t="s">
+      <c r="CX94" t="s">
+        <v>5</v>
+      </c>
+      <c r="CY94" t="s">
+        <v>6</v>
+      </c>
+      <c r="CZ94" t="s">
         <v>21</v>
       </c>
-      <c r="DI94" t="s">
-        <v>8</v>
-      </c>
-      <c r="DJ94" t="s">
+      <c r="DE94" t="s">
+        <v>8</v>
+      </c>
+      <c r="DF94" t="s">
         <v>11</v>
       </c>
     </row>
@@ -3683,19 +3620,19 @@
       <c r="C95" t="s">
         <v>31</v>
       </c>
+      <c r="CY95" t="s">
+        <v>5</v>
+      </c>
+      <c r="CZ95" t="s">
+        <v>6</v>
+      </c>
+      <c r="DA95" t="s">
+        <v>8</v>
+      </c>
       <c r="DB95" t="s">
-        <v>5</v>
-      </c>
-      <c r="DC95" t="s">
-        <v>6</v>
-      </c>
-      <c r="DD95" t="s">
-        <v>8</v>
-      </c>
-      <c r="DE95" t="s">
-        <v>10</v>
-      </c>
-      <c r="DJ95" t="s">
+        <v>10</v>
+      </c>
+      <c r="DF95" t="s">
         <v>11</v>
       </c>
     </row>
@@ -3709,22 +3646,19 @@
       <c r="C96" t="s">
         <v>32</v>
       </c>
+      <c r="CZ96" t="s">
+        <v>5</v>
+      </c>
+      <c r="DA96" t="s">
+        <v>6</v>
+      </c>
+      <c r="DB96" t="s">
+        <v>8</v>
+      </c>
       <c r="DC96" t="s">
-        <v>5</v>
-      </c>
-      <c r="DD96" t="s">
-        <v>6</v>
-      </c>
-      <c r="DE96" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="DF96" t="s">
-        <v>8</v>
-      </c>
-      <c r="DG96" t="s">
-        <v>10</v>
-      </c>
-      <c r="DJ96" t="s">
         <v>11</v>
       </c>
     </row>
@@ -3738,22 +3672,22 @@
       <c r="C97" t="s">
         <v>33</v>
       </c>
+      <c r="DC97" t="s">
+        <v>5</v>
+      </c>
+      <c r="DD97" t="s">
+        <v>6</v>
+      </c>
+      <c r="DE97" t="s">
+        <v>8</v>
+      </c>
+      <c r="DF97" t="s">
+        <v>8</v>
+      </c>
       <c r="DG97" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="DH97" t="s">
-        <v>6</v>
-      </c>
-      <c r="DI97" t="s">
-        <v>8</v>
-      </c>
-      <c r="DJ97" t="s">
-        <v>8</v>
-      </c>
-      <c r="DK97" t="s">
-        <v>8</v>
-      </c>
-      <c r="DL97" t="s">
         <v>11</v>
       </c>
     </row>
@@ -3767,25 +3701,25 @@
       <c r="C98" t="s">
         <v>34</v>
       </c>
+      <c r="DD98" t="s">
+        <v>5</v>
+      </c>
+      <c r="DE98" t="s">
+        <v>6</v>
+      </c>
+      <c r="DF98" t="s">
+        <v>21</v>
+      </c>
       <c r="DH98" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="DI98" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="DJ98" t="s">
-        <v>21</v>
-      </c>
-      <c r="DL98" t="s">
-        <v>8</v>
-      </c>
-      <c r="DM98" t="s">
-        <v>8</v>
-      </c>
-      <c r="DN98" t="s">
-        <v>8</v>
-      </c>
-      <c r="DO98" t="s">
+        <v>8</v>
+      </c>
+      <c r="DK98" t="s">
         <v>11</v>
       </c>
     </row>
@@ -3799,19 +3733,19 @@
       <c r="C99" t="s">
         <v>35</v>
       </c>
-      <c r="DI99" t="s">
-        <v>5</v>
-      </c>
-      <c r="DJ99" t="s">
-        <v>6</v>
+      <c r="DE99" t="s">
+        <v>5</v>
+      </c>
+      <c r="DF99" t="s">
+        <v>6</v>
+      </c>
+      <c r="DG99" t="s">
+        <v>8</v>
+      </c>
+      <c r="DH99" t="s">
+        <v>10</v>
       </c>
       <c r="DK99" t="s">
-        <v>8</v>
-      </c>
-      <c r="DL99" t="s">
-        <v>10</v>
-      </c>
-      <c r="DO99" t="s">
         <v>11</v>
       </c>
     </row>
@@ -3825,16 +3759,16 @@
       <c r="C100" t="s">
         <v>36</v>
       </c>
-      <c r="DJ100" t="s">
-        <v>5</v>
-      </c>
-      <c r="DL100" t="s">
-        <v>8</v>
-      </c>
-      <c r="DM100" t="s">
-        <v>10</v>
-      </c>
-      <c r="DO100" t="s">
+      <c r="DF100" t="s">
+        <v>5</v>
+      </c>
+      <c r="DH100" t="s">
+        <v>8</v>
+      </c>
+      <c r="DI100" t="s">
+        <v>10</v>
+      </c>
+      <c r="DK100" t="s">
         <v>11</v>
       </c>
     </row>
@@ -3848,19 +3782,19 @@
       <c r="C101" t="s">
         <v>37</v>
       </c>
+      <c r="DG101" t="s">
+        <v>5</v>
+      </c>
+      <c r="DH101" t="s">
+        <v>6</v>
+      </c>
+      <c r="DI101" t="s">
+        <v>8</v>
+      </c>
+      <c r="DJ101" t="s">
+        <v>10</v>
+      </c>
       <c r="DK101" t="s">
-        <v>5</v>
-      </c>
-      <c r="DL101" t="s">
-        <v>6</v>
-      </c>
-      <c r="DM101" t="s">
-        <v>8</v>
-      </c>
-      <c r="DN101" t="s">
-        <v>10</v>
-      </c>
-      <c r="DO101" t="s">
         <v>11</v>
       </c>
     </row>
@@ -3874,19 +3808,19 @@
       <c r="C102" t="s">
         <v>38</v>
       </c>
+      <c r="DH102" t="s">
+        <v>5</v>
+      </c>
+      <c r="DI102" t="s">
+        <v>6</v>
+      </c>
+      <c r="DJ102" t="s">
+        <v>8</v>
+      </c>
+      <c r="DK102" t="s">
+        <v>10</v>
+      </c>
       <c r="DL102" t="s">
-        <v>5</v>
-      </c>
-      <c r="DM102" t="s">
-        <v>6</v>
-      </c>
-      <c r="DN102" t="s">
-        <v>8</v>
-      </c>
-      <c r="DO102" t="s">
-        <v>10</v>
-      </c>
-      <c r="DP102" t="s">
         <v>11</v>
       </c>
     </row>
@@ -3900,16 +3834,16 @@
       <c r="C103" t="s">
         <v>39</v>
       </c>
-      <c r="DM103" t="s">
-        <v>5</v>
-      </c>
-      <c r="DN103" t="s">
-        <v>6</v>
-      </c>
-      <c r="DO103" t="s">
-        <v>8</v>
-      </c>
-      <c r="DP103" t="s">
+      <c r="DI103" t="s">
+        <v>5</v>
+      </c>
+      <c r="DJ103" t="s">
+        <v>6</v>
+      </c>
+      <c r="DK103" t="s">
+        <v>8</v>
+      </c>
+      <c r="DL103" t="s">
         <v>11</v>
       </c>
     </row>
@@ -3923,16 +3857,16 @@
       <c r="C104" t="s">
         <v>40</v>
       </c>
-      <c r="DN104" t="s">
-        <v>5</v>
-      </c>
-      <c r="DO104" t="s">
-        <v>6</v>
-      </c>
-      <c r="DP104" t="s">
-        <v>8</v>
-      </c>
-      <c r="DQ104" t="s">
+      <c r="DJ104" t="s">
+        <v>5</v>
+      </c>
+      <c r="DK104" t="s">
+        <v>6</v>
+      </c>
+      <c r="DL104" t="s">
+        <v>8</v>
+      </c>
+      <c r="DM104" t="s">
         <v>11</v>
       </c>
     </row>
@@ -3946,16 +3880,16 @@
       <c r="C105" t="s">
         <v>41</v>
       </c>
-      <c r="DO105" t="s">
-        <v>5</v>
-      </c>
-      <c r="DP105" t="s">
-        <v>6</v>
-      </c>
-      <c r="DQ105" t="s">
-        <v>8</v>
-      </c>
-      <c r="DR105" t="s">
+      <c r="DK105" t="s">
+        <v>5</v>
+      </c>
+      <c r="DL105" t="s">
+        <v>6</v>
+      </c>
+      <c r="DM105" t="s">
+        <v>8</v>
+      </c>
+      <c r="DN105" t="s">
         <v>11</v>
       </c>
     </row>
@@ -3969,16 +3903,16 @@
       <c r="C106" t="s">
         <v>42</v>
       </c>
-      <c r="DP106" t="s">
-        <v>5</v>
-      </c>
-      <c r="DQ106" t="s">
-        <v>6</v>
-      </c>
-      <c r="DR106" t="s">
-        <v>8</v>
-      </c>
-      <c r="DS106" t="s">
+      <c r="DL106" t="s">
+        <v>5</v>
+      </c>
+      <c r="DM106" t="s">
+        <v>6</v>
+      </c>
+      <c r="DN106" t="s">
+        <v>8</v>
+      </c>
+      <c r="DO106" t="s">
         <v>11</v>
       </c>
     </row>
@@ -3992,16 +3926,16 @@
       <c r="C107" t="s">
         <v>43</v>
       </c>
-      <c r="DQ107" t="s">
-        <v>5</v>
-      </c>
-      <c r="DR107" t="s">
-        <v>6</v>
-      </c>
-      <c r="DS107" t="s">
-        <v>8</v>
-      </c>
-      <c r="DT107" t="s">
+      <c r="DM107" t="s">
+        <v>5</v>
+      </c>
+      <c r="DN107" t="s">
+        <v>6</v>
+      </c>
+      <c r="DO107" t="s">
+        <v>8</v>
+      </c>
+      <c r="DP107" t="s">
         <v>11</v>
       </c>
     </row>
@@ -4015,16 +3949,16 @@
       <c r="C108" t="s">
         <v>44</v>
       </c>
-      <c r="DR108" t="s">
-        <v>5</v>
-      </c>
-      <c r="DS108" t="s">
-        <v>6</v>
-      </c>
-      <c r="DT108" t="s">
-        <v>8</v>
-      </c>
-      <c r="DU108" t="s">
+      <c r="DN108" t="s">
+        <v>5</v>
+      </c>
+      <c r="DO108" t="s">
+        <v>6</v>
+      </c>
+      <c r="DP108" t="s">
+        <v>8</v>
+      </c>
+      <c r="DQ108" t="s">
         <v>11</v>
       </c>
     </row>
@@ -4038,16 +3972,16 @@
       <c r="C109" t="s">
         <v>45</v>
       </c>
-      <c r="DS109" t="s">
-        <v>5</v>
-      </c>
-      <c r="DT109" t="s">
-        <v>6</v>
-      </c>
-      <c r="DU109" t="s">
-        <v>8</v>
-      </c>
-      <c r="DV109" t="s">
+      <c r="DO109" t="s">
+        <v>5</v>
+      </c>
+      <c r="DP109" t="s">
+        <v>6</v>
+      </c>
+      <c r="DQ109" t="s">
+        <v>8</v>
+      </c>
+      <c r="DR109" t="s">
         <v>11</v>
       </c>
     </row>

--- a/project/outputs_xlsx_solution/test33.4-wide-NF-1.xlsx
+++ b/project/outputs_xlsx_solution/test33.4-wide-NF-1.xlsx
@@ -936,6 +936,18 @@
       <c r="DR1">
         <v>119</v>
       </c>
+      <c r="DS1">
+        <v>120</v>
+      </c>
+      <c r="DT1">
+        <v>121</v>
+      </c>
+      <c r="DU1">
+        <v>122</v>
+      </c>
+      <c r="DV1">
+        <v>123</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2">
@@ -2007,6 +2019,9 @@
       <c r="AT40" t="s">
         <v>5</v>
       </c>
+      <c r="AU40" t="s">
+        <v>6</v>
+      </c>
       <c r="AV40" t="s">
         <v>8</v>
       </c>
@@ -2027,22 +2042,22 @@
       <c r="C41" t="s">
         <v>18</v>
       </c>
-      <c r="AU41" t="s">
-        <v>5</v>
-      </c>
-      <c r="AV41" t="s">
-        <v>6</v>
-      </c>
       <c r="AW41" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AX41" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AY41" t="s">
         <v>8</v>
       </c>
       <c r="AZ41" t="s">
+        <v>8</v>
+      </c>
+      <c r="BA41" t="s">
+        <v>8</v>
+      </c>
+      <c r="BB41" t="s">
         <v>11</v>
       </c>
     </row>
@@ -2056,25 +2071,25 @@
       <c r="C42" t="s">
         <v>19</v>
       </c>
-      <c r="AV42" t="s">
-        <v>5</v>
-      </c>
-      <c r="AW42" t="s">
-        <v>6</v>
-      </c>
       <c r="AX42" t="s">
+        <v>5</v>
+      </c>
+      <c r="AY42" t="s">
+        <v>6</v>
+      </c>
+      <c r="AZ42" t="s">
         <v>21</v>
       </c>
-      <c r="AZ42" t="s">
-        <v>8</v>
-      </c>
-      <c r="BA42" t="s">
-        <v>8</v>
-      </c>
       <c r="BB42" t="s">
         <v>8</v>
       </c>
       <c r="BC42" t="s">
+        <v>8</v>
+      </c>
+      <c r="BD42" t="s">
+        <v>8</v>
+      </c>
+      <c r="BE42" t="s">
         <v>11</v>
       </c>
     </row>
@@ -2088,24 +2103,18 @@
       <c r="C43" t="s">
         <v>20</v>
       </c>
-      <c r="AW43" t="s">
-        <v>5</v>
-      </c>
-      <c r="AX43" t="s">
-        <v>6</v>
-      </c>
       <c r="AY43" t="s">
+        <v>5</v>
+      </c>
+      <c r="AZ43" t="s">
+        <v>6</v>
+      </c>
+      <c r="BA43" t="s">
         <v>21</v>
       </c>
-      <c r="BC43" t="s">
+      <c r="BE43" t="s">
         <v>26</v>
       </c>
-      <c r="BD43" t="s">
-        <v>8</v>
-      </c>
-      <c r="BE43" t="s">
-        <v>8</v>
-      </c>
       <c r="BF43" t="s">
         <v>8</v>
       </c>
@@ -2113,6 +2122,12 @@
         <v>8</v>
       </c>
       <c r="BH43" t="s">
+        <v>8</v>
+      </c>
+      <c r="BI43" t="s">
+        <v>8</v>
+      </c>
+      <c r="BJ43" t="s">
         <v>11</v>
       </c>
     </row>
@@ -2126,17 +2141,11 @@
       <c r="C44" t="s">
         <v>22</v>
       </c>
-      <c r="AX44" t="s">
-        <v>5</v>
-      </c>
-      <c r="AY44" t="s">
-        <v>6</v>
-      </c>
       <c r="AZ44" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="BA44" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BB44" t="s">
         <v>8</v>
@@ -2145,9 +2154,15 @@
         <v>8</v>
       </c>
       <c r="BD44" t="s">
-        <v>10</v>
-      </c>
-      <c r="BH44" t="s">
+        <v>8</v>
+      </c>
+      <c r="BE44" t="s">
+        <v>8</v>
+      </c>
+      <c r="BF44" t="s">
+        <v>10</v>
+      </c>
+      <c r="BJ44" t="s">
         <v>11</v>
       </c>
     </row>
@@ -2161,17 +2176,11 @@
       <c r="C45" t="s">
         <v>23</v>
       </c>
-      <c r="AY45" t="s">
-        <v>5</v>
-      </c>
-      <c r="AZ45" t="s">
-        <v>6</v>
-      </c>
       <c r="BA45" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="BB45" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BC45" t="s">
         <v>8</v>
@@ -2186,9 +2195,15 @@
         <v>8</v>
       </c>
       <c r="BG45" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BH45" t="s">
+        <v>8</v>
+      </c>
+      <c r="BI45" t="s">
+        <v>10</v>
+      </c>
+      <c r="BJ45" t="s">
         <v>11</v>
       </c>
     </row>
@@ -2202,19 +2217,19 @@
       <c r="C46" t="s">
         <v>24</v>
       </c>
-      <c r="AZ46" t="s">
-        <v>5</v>
-      </c>
-      <c r="BA46" t="s">
-        <v>6</v>
-      </c>
       <c r="BB46" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="BC46" t="s">
-        <v>10</v>
-      </c>
-      <c r="BH46" t="s">
+        <v>6</v>
+      </c>
+      <c r="BD46" t="s">
+        <v>8</v>
+      </c>
+      <c r="BE46" t="s">
+        <v>10</v>
+      </c>
+      <c r="BJ46" t="s">
         <v>11</v>
       </c>
     </row>
@@ -2228,19 +2243,19 @@
       <c r="C47" t="s">
         <v>16</v>
       </c>
-      <c r="BA47" t="s">
-        <v>5</v>
-      </c>
-      <c r="BB47" t="s">
-        <v>6</v>
-      </c>
       <c r="BC47" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="BD47" t="s">
-        <v>10</v>
-      </c>
-      <c r="BI47" t="s">
+        <v>6</v>
+      </c>
+      <c r="BE47" t="s">
+        <v>8</v>
+      </c>
+      <c r="BF47" t="s">
+        <v>10</v>
+      </c>
+      <c r="BK47" t="s">
         <v>11</v>
       </c>
     </row>
@@ -2254,19 +2269,19 @@
       <c r="C48" t="s">
         <v>25</v>
       </c>
-      <c r="BB48" t="s">
-        <v>5</v>
-      </c>
-      <c r="BC48" t="s">
-        <v>6</v>
-      </c>
       <c r="BD48" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="BE48" t="s">
-        <v>10</v>
-      </c>
-      <c r="BI48" t="s">
+        <v>6</v>
+      </c>
+      <c r="BF48" t="s">
+        <v>8</v>
+      </c>
+      <c r="BG48" t="s">
+        <v>10</v>
+      </c>
+      <c r="BK48" t="s">
         <v>11</v>
       </c>
     </row>
@@ -2280,19 +2295,19 @@
       <c r="C49" t="s">
         <v>27</v>
       </c>
-      <c r="BC49" t="s">
-        <v>5</v>
-      </c>
-      <c r="BD49" t="s">
-        <v>6</v>
-      </c>
       <c r="BE49" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="BF49" t="s">
-        <v>10</v>
-      </c>
-      <c r="BI49" t="s">
+        <v>6</v>
+      </c>
+      <c r="BG49" t="s">
+        <v>8</v>
+      </c>
+      <c r="BH49" t="s">
+        <v>10</v>
+      </c>
+      <c r="BK49" t="s">
         <v>11</v>
       </c>
     </row>
@@ -2306,24 +2321,18 @@
       <c r="C50" t="s">
         <v>28</v>
       </c>
-      <c r="BD50" t="s">
-        <v>5</v>
-      </c>
-      <c r="BE50" t="s">
-        <v>6</v>
-      </c>
       <c r="BF50" t="s">
+        <v>5</v>
+      </c>
+      <c r="BG50" t="s">
+        <v>6</v>
+      </c>
+      <c r="BH50" t="s">
         <v>26</v>
       </c>
-      <c r="BG50" t="s">
+      <c r="BI50" t="s">
         <v>26</v>
       </c>
-      <c r="BH50" t="s">
-        <v>8</v>
-      </c>
-      <c r="BI50" t="s">
-        <v>8</v>
-      </c>
       <c r="BJ50" t="s">
         <v>8</v>
       </c>
@@ -2331,6 +2340,12 @@
         <v>8</v>
       </c>
       <c r="BL50" t="s">
+        <v>8</v>
+      </c>
+      <c r="BM50" t="s">
+        <v>8</v>
+      </c>
+      <c r="BN50" t="s">
         <v>11</v>
       </c>
     </row>
@@ -2344,25 +2359,25 @@
       <c r="C51" t="s">
         <v>29</v>
       </c>
-      <c r="BE51" t="s">
-        <v>5</v>
-      </c>
-      <c r="BF51" t="s">
-        <v>6</v>
-      </c>
       <c r="BG51" t="s">
+        <v>5</v>
+      </c>
+      <c r="BH51" t="s">
+        <v>6</v>
+      </c>
+      <c r="BI51" t="s">
         <v>21</v>
       </c>
-      <c r="BL51" t="s">
-        <v>8</v>
-      </c>
-      <c r="BM51" t="s">
-        <v>8</v>
-      </c>
       <c r="BN51" t="s">
         <v>8</v>
       </c>
       <c r="BO51" t="s">
+        <v>8</v>
+      </c>
+      <c r="BP51" t="s">
+        <v>8</v>
+      </c>
+      <c r="BQ51" t="s">
         <v>11</v>
       </c>
     </row>
@@ -2376,19 +2391,19 @@
       <c r="C52" t="s">
         <v>30</v>
       </c>
-      <c r="BF52" t="s">
-        <v>5</v>
-      </c>
-      <c r="BG52" t="s">
-        <v>6</v>
-      </c>
       <c r="BH52" t="s">
+        <v>5</v>
+      </c>
+      <c r="BI52" t="s">
+        <v>6</v>
+      </c>
+      <c r="BJ52" t="s">
         <v>21</v>
       </c>
-      <c r="BO52" t="s">
-        <v>8</v>
-      </c>
-      <c r="BP52" t="s">
+      <c r="BQ52" t="s">
+        <v>8</v>
+      </c>
+      <c r="BR52" t="s">
         <v>11</v>
       </c>
     </row>
@@ -2402,19 +2417,19 @@
       <c r="C53" t="s">
         <v>31</v>
       </c>
-      <c r="BG53" t="s">
-        <v>5</v>
-      </c>
-      <c r="BH53" t="s">
-        <v>6</v>
-      </c>
       <c r="BI53" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="BJ53" t="s">
-        <v>10</v>
-      </c>
-      <c r="BP53" t="s">
+        <v>6</v>
+      </c>
+      <c r="BK53" t="s">
+        <v>8</v>
+      </c>
+      <c r="BL53" t="s">
+        <v>10</v>
+      </c>
+      <c r="BR53" t="s">
         <v>11</v>
       </c>
     </row>
@@ -2428,19 +2443,19 @@
       <c r="C54" t="s">
         <v>32</v>
       </c>
-      <c r="BH54" t="s">
-        <v>5</v>
-      </c>
-      <c r="BI54" t="s">
-        <v>6</v>
-      </c>
       <c r="BJ54" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="BK54" t="s">
-        <v>10</v>
-      </c>
-      <c r="BP54" t="s">
+        <v>6</v>
+      </c>
+      <c r="BL54" t="s">
+        <v>8</v>
+      </c>
+      <c r="BM54" t="s">
+        <v>10</v>
+      </c>
+      <c r="BR54" t="s">
         <v>11</v>
       </c>
     </row>
@@ -2454,19 +2469,19 @@
       <c r="C55" t="s">
         <v>27</v>
       </c>
-      <c r="BI55" t="s">
-        <v>5</v>
-      </c>
-      <c r="BJ55" t="s">
-        <v>6</v>
-      </c>
       <c r="BK55" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="BL55" t="s">
-        <v>10</v>
-      </c>
-      <c r="BP55" t="s">
+        <v>6</v>
+      </c>
+      <c r="BM55" t="s">
+        <v>8</v>
+      </c>
+      <c r="BN55" t="s">
+        <v>10</v>
+      </c>
+      <c r="BR55" t="s">
         <v>11</v>
       </c>
     </row>
@@ -2480,17 +2495,11 @@
       <c r="C56" t="s">
         <v>28</v>
       </c>
-      <c r="BJ56" t="s">
-        <v>5</v>
-      </c>
-      <c r="BK56" t="s">
-        <v>6</v>
-      </c>
       <c r="BL56" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="BM56" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BN56" t="s">
         <v>8</v>
@@ -2499,9 +2508,15 @@
         <v>8</v>
       </c>
       <c r="BP56" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BQ56" t="s">
+        <v>8</v>
+      </c>
+      <c r="BR56" t="s">
+        <v>10</v>
+      </c>
+      <c r="BS56" t="s">
         <v>11</v>
       </c>
     </row>
@@ -2515,25 +2530,25 @@
       <c r="C57" t="s">
         <v>29</v>
       </c>
-      <c r="BK57" t="s">
-        <v>5</v>
-      </c>
-      <c r="BL57" t="s">
-        <v>6</v>
-      </c>
       <c r="BM57" t="s">
+        <v>5</v>
+      </c>
+      <c r="BN57" t="s">
+        <v>6</v>
+      </c>
+      <c r="BO57" t="s">
         <v>21</v>
       </c>
-      <c r="BP57" t="s">
-        <v>8</v>
-      </c>
-      <c r="BQ57" t="s">
-        <v>8</v>
-      </c>
       <c r="BR57" t="s">
         <v>8</v>
       </c>
       <c r="BS57" t="s">
+        <v>8</v>
+      </c>
+      <c r="BT57" t="s">
+        <v>8</v>
+      </c>
+      <c r="BU57" t="s">
         <v>11</v>
       </c>
     </row>
@@ -2547,19 +2562,19 @@
       <c r="C58" t="s">
         <v>30</v>
       </c>
-      <c r="BL58" t="s">
-        <v>5</v>
-      </c>
-      <c r="BM58" t="s">
-        <v>6</v>
-      </c>
       <c r="BN58" t="s">
+        <v>5</v>
+      </c>
+      <c r="BO58" t="s">
+        <v>6</v>
+      </c>
+      <c r="BP58" t="s">
         <v>21</v>
       </c>
-      <c r="BS58" t="s">
-        <v>8</v>
-      </c>
-      <c r="BT58" t="s">
+      <c r="BU58" t="s">
+        <v>8</v>
+      </c>
+      <c r="BV58" t="s">
         <v>11</v>
       </c>
     </row>
@@ -2573,19 +2588,19 @@
       <c r="C59" t="s">
         <v>31</v>
       </c>
-      <c r="BM59" t="s">
-        <v>5</v>
-      </c>
-      <c r="BN59" t="s">
-        <v>6</v>
-      </c>
       <c r="BO59" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="BP59" t="s">
-        <v>10</v>
-      </c>
-      <c r="BT59" t="s">
+        <v>6</v>
+      </c>
+      <c r="BQ59" t="s">
+        <v>8</v>
+      </c>
+      <c r="BR59" t="s">
+        <v>10</v>
+      </c>
+      <c r="BV59" t="s">
         <v>11</v>
       </c>
     </row>
@@ -2599,19 +2614,19 @@
       <c r="C60" t="s">
         <v>32</v>
       </c>
-      <c r="BN60" t="s">
-        <v>5</v>
-      </c>
-      <c r="BO60" t="s">
-        <v>6</v>
-      </c>
       <c r="BP60" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="BQ60" t="s">
-        <v>10</v>
-      </c>
-      <c r="BT60" t="s">
+        <v>6</v>
+      </c>
+      <c r="BR60" t="s">
+        <v>8</v>
+      </c>
+      <c r="BS60" t="s">
+        <v>10</v>
+      </c>
+      <c r="BV60" t="s">
         <v>11</v>
       </c>
     </row>
@@ -2625,19 +2640,19 @@
       <c r="C61" t="s">
         <v>27</v>
       </c>
-      <c r="BO61" t="s">
-        <v>5</v>
-      </c>
-      <c r="BP61" t="s">
-        <v>6</v>
-      </c>
       <c r="BQ61" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="BR61" t="s">
-        <v>10</v>
+        <v>6</v>
+      </c>
+      <c r="BS61" t="s">
+        <v>8</v>
       </c>
       <c r="BT61" t="s">
+        <v>10</v>
+      </c>
+      <c r="BV61" t="s">
         <v>11</v>
       </c>
     </row>
@@ -2651,17 +2666,11 @@
       <c r="C62" t="s">
         <v>28</v>
       </c>
-      <c r="BP62" t="s">
-        <v>5</v>
-      </c>
-      <c r="BQ62" t="s">
-        <v>6</v>
-      </c>
       <c r="BR62" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="BS62" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BT62" t="s">
         <v>8</v>
@@ -2670,6 +2679,12 @@
         <v>8</v>
       </c>
       <c r="BV62" t="s">
+        <v>8</v>
+      </c>
+      <c r="BW62" t="s">
+        <v>8</v>
+      </c>
+      <c r="BX62" t="s">
         <v>11</v>
       </c>
     </row>
@@ -2683,25 +2698,25 @@
       <c r="C63" t="s">
         <v>29</v>
       </c>
-      <c r="BQ63" t="s">
-        <v>5</v>
-      </c>
-      <c r="BR63" t="s">
-        <v>6</v>
-      </c>
       <c r="BS63" t="s">
+        <v>5</v>
+      </c>
+      <c r="BT63" t="s">
+        <v>6</v>
+      </c>
+      <c r="BU63" t="s">
         <v>21</v>
       </c>
-      <c r="BV63" t="s">
-        <v>8</v>
-      </c>
-      <c r="BW63" t="s">
-        <v>8</v>
-      </c>
       <c r="BX63" t="s">
         <v>8</v>
       </c>
       <c r="BY63" t="s">
+        <v>8</v>
+      </c>
+      <c r="BZ63" t="s">
+        <v>8</v>
+      </c>
+      <c r="CA63" t="s">
         <v>11</v>
       </c>
     </row>
@@ -2715,19 +2730,19 @@
       <c r="C64" t="s">
         <v>30</v>
       </c>
-      <c r="BR64" t="s">
-        <v>5</v>
-      </c>
-      <c r="BS64" t="s">
-        <v>6</v>
-      </c>
       <c r="BT64" t="s">
+        <v>5</v>
+      </c>
+      <c r="BU64" t="s">
+        <v>6</v>
+      </c>
+      <c r="BV64" t="s">
         <v>21</v>
       </c>
-      <c r="BY64" t="s">
-        <v>8</v>
-      </c>
-      <c r="BZ64" t="s">
+      <c r="CA64" t="s">
+        <v>8</v>
+      </c>
+      <c r="CB64" t="s">
         <v>11</v>
       </c>
     </row>
@@ -2741,19 +2756,19 @@
       <c r="C65" t="s">
         <v>31</v>
       </c>
-      <c r="BS65" t="s">
-        <v>5</v>
-      </c>
-      <c r="BT65" t="s">
-        <v>6</v>
-      </c>
       <c r="BU65" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="BV65" t="s">
-        <v>10</v>
-      </c>
-      <c r="BZ65" t="s">
+        <v>6</v>
+      </c>
+      <c r="BW65" t="s">
+        <v>8</v>
+      </c>
+      <c r="BX65" t="s">
+        <v>10</v>
+      </c>
+      <c r="CB65" t="s">
         <v>11</v>
       </c>
     </row>
@@ -2767,19 +2782,19 @@
       <c r="C66" t="s">
         <v>32</v>
       </c>
-      <c r="BT66" t="s">
-        <v>5</v>
-      </c>
-      <c r="BU66" t="s">
-        <v>6</v>
-      </c>
       <c r="BV66" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="BW66" t="s">
-        <v>10</v>
-      </c>
-      <c r="BZ66" t="s">
+        <v>6</v>
+      </c>
+      <c r="BX66" t="s">
+        <v>8</v>
+      </c>
+      <c r="BY66" t="s">
+        <v>10</v>
+      </c>
+      <c r="CB66" t="s">
         <v>11</v>
       </c>
     </row>
@@ -2793,22 +2808,22 @@
       <c r="C67" t="s">
         <v>33</v>
       </c>
-      <c r="BW67" t="s">
-        <v>5</v>
-      </c>
-      <c r="BX67" t="s">
-        <v>6</v>
-      </c>
       <c r="BY67" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="BZ67" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="CA67" t="s">
         <v>8</v>
       </c>
       <c r="CB67" t="s">
+        <v>8</v>
+      </c>
+      <c r="CC67" t="s">
+        <v>8</v>
+      </c>
+      <c r="CD67" t="s">
         <v>11</v>
       </c>
     </row>
@@ -2822,25 +2837,25 @@
       <c r="C68" t="s">
         <v>34</v>
       </c>
-      <c r="BX68" t="s">
-        <v>5</v>
-      </c>
-      <c r="BY68" t="s">
-        <v>6</v>
-      </c>
       <c r="BZ68" t="s">
+        <v>5</v>
+      </c>
+      <c r="CA68" t="s">
+        <v>6</v>
+      </c>
+      <c r="CB68" t="s">
         <v>21</v>
       </c>
-      <c r="CB68" t="s">
-        <v>8</v>
-      </c>
-      <c r="CC68" t="s">
-        <v>8</v>
-      </c>
       <c r="CD68" t="s">
         <v>8</v>
       </c>
       <c r="CE68" t="s">
+        <v>8</v>
+      </c>
+      <c r="CF68" t="s">
+        <v>8</v>
+      </c>
+      <c r="CG68" t="s">
         <v>11</v>
       </c>
     </row>
@@ -2854,19 +2869,19 @@
       <c r="C69" t="s">
         <v>35</v>
       </c>
-      <c r="BY69" t="s">
-        <v>5</v>
-      </c>
-      <c r="BZ69" t="s">
-        <v>6</v>
-      </c>
       <c r="CA69" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="CB69" t="s">
-        <v>10</v>
-      </c>
-      <c r="CE69" t="s">
+        <v>6</v>
+      </c>
+      <c r="CC69" t="s">
+        <v>8</v>
+      </c>
+      <c r="CD69" t="s">
+        <v>10</v>
+      </c>
+      <c r="CG69" t="s">
         <v>11</v>
       </c>
     </row>
@@ -2880,19 +2895,19 @@
       <c r="C70" t="s">
         <v>36</v>
       </c>
-      <c r="BZ70" t="s">
-        <v>5</v>
-      </c>
-      <c r="CA70" t="s">
-        <v>6</v>
-      </c>
       <c r="CB70" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="CC70" t="s">
-        <v>10</v>
+        <v>6</v>
+      </c>
+      <c r="CD70" t="s">
+        <v>8</v>
       </c>
       <c r="CE70" t="s">
+        <v>10</v>
+      </c>
+      <c r="CG70" t="s">
         <v>11</v>
       </c>
     </row>
@@ -2906,22 +2921,22 @@
       <c r="C71" t="s">
         <v>18</v>
       </c>
-      <c r="CA71" t="s">
-        <v>5</v>
-      </c>
-      <c r="CB71" t="s">
-        <v>6</v>
-      </c>
       <c r="CC71" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="CD71" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="CE71" t="s">
         <v>8</v>
       </c>
       <c r="CF71" t="s">
+        <v>8</v>
+      </c>
+      <c r="CG71" t="s">
+        <v>8</v>
+      </c>
+      <c r="CH71" t="s">
         <v>11</v>
       </c>
     </row>
@@ -2935,25 +2950,25 @@
       <c r="C72" t="s">
         <v>19</v>
       </c>
-      <c r="CB72" t="s">
-        <v>5</v>
-      </c>
-      <c r="CC72" t="s">
-        <v>6</v>
-      </c>
       <c r="CD72" t="s">
+        <v>5</v>
+      </c>
+      <c r="CE72" t="s">
+        <v>6</v>
+      </c>
+      <c r="CF72" t="s">
         <v>21</v>
       </c>
-      <c r="CF72" t="s">
-        <v>8</v>
-      </c>
-      <c r="CG72" t="s">
-        <v>8</v>
-      </c>
       <c r="CH72" t="s">
         <v>8</v>
       </c>
       <c r="CI72" t="s">
+        <v>8</v>
+      </c>
+      <c r="CJ72" t="s">
+        <v>8</v>
+      </c>
+      <c r="CK72" t="s">
         <v>11</v>
       </c>
     </row>
@@ -2967,24 +2982,18 @@
       <c r="C73" t="s">
         <v>20</v>
       </c>
-      <c r="CC73" t="s">
-        <v>5</v>
-      </c>
-      <c r="CD73" t="s">
-        <v>6</v>
-      </c>
       <c r="CE73" t="s">
+        <v>5</v>
+      </c>
+      <c r="CF73" t="s">
+        <v>6</v>
+      </c>
+      <c r="CG73" t="s">
         <v>21</v>
       </c>
-      <c r="CI73" t="s">
+      <c r="CK73" t="s">
         <v>26</v>
       </c>
-      <c r="CJ73" t="s">
-        <v>8</v>
-      </c>
-      <c r="CK73" t="s">
-        <v>8</v>
-      </c>
       <c r="CL73" t="s">
         <v>8</v>
       </c>
@@ -2992,6 +3001,12 @@
         <v>8</v>
       </c>
       <c r="CN73" t="s">
+        <v>8</v>
+      </c>
+      <c r="CO73" t="s">
+        <v>8</v>
+      </c>
+      <c r="CP73" t="s">
         <v>11</v>
       </c>
     </row>
@@ -3005,17 +3020,11 @@
       <c r="C74" t="s">
         <v>22</v>
       </c>
-      <c r="CD74" t="s">
-        <v>5</v>
-      </c>
-      <c r="CE74" t="s">
-        <v>6</v>
-      </c>
       <c r="CF74" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="CG74" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="CH74" t="s">
         <v>8</v>
@@ -3024,9 +3033,15 @@
         <v>8</v>
       </c>
       <c r="CJ74" t="s">
-        <v>10</v>
-      </c>
-      <c r="CN74" t="s">
+        <v>8</v>
+      </c>
+      <c r="CK74" t="s">
+        <v>8</v>
+      </c>
+      <c r="CL74" t="s">
+        <v>10</v>
+      </c>
+      <c r="CP74" t="s">
         <v>11</v>
       </c>
     </row>
@@ -3040,17 +3055,11 @@
       <c r="C75" t="s">
         <v>23</v>
       </c>
-      <c r="CE75" t="s">
-        <v>5</v>
-      </c>
-      <c r="CF75" t="s">
-        <v>6</v>
-      </c>
       <c r="CG75" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="CH75" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="CI75" t="s">
         <v>8</v>
@@ -3065,9 +3074,15 @@
         <v>8</v>
       </c>
       <c r="CM75" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="CN75" t="s">
+        <v>8</v>
+      </c>
+      <c r="CO75" t="s">
+        <v>10</v>
+      </c>
+      <c r="CP75" t="s">
         <v>11</v>
       </c>
     </row>
@@ -3081,19 +3096,19 @@
       <c r="C76" t="s">
         <v>24</v>
       </c>
-      <c r="CF76" t="s">
-        <v>5</v>
-      </c>
-      <c r="CG76" t="s">
-        <v>6</v>
-      </c>
       <c r="CH76" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="CI76" t="s">
-        <v>10</v>
-      </c>
-      <c r="CN76" t="s">
+        <v>6</v>
+      </c>
+      <c r="CJ76" t="s">
+        <v>8</v>
+      </c>
+      <c r="CK76" t="s">
+        <v>10</v>
+      </c>
+      <c r="CP76" t="s">
         <v>11</v>
       </c>
     </row>
@@ -3107,19 +3122,19 @@
       <c r="C77" t="s">
         <v>16</v>
       </c>
-      <c r="CG77" t="s">
-        <v>5</v>
-      </c>
-      <c r="CH77" t="s">
-        <v>6</v>
-      </c>
       <c r="CI77" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="CJ77" t="s">
-        <v>10</v>
-      </c>
-      <c r="CO77" t="s">
+        <v>6</v>
+      </c>
+      <c r="CK77" t="s">
+        <v>8</v>
+      </c>
+      <c r="CL77" t="s">
+        <v>10</v>
+      </c>
+      <c r="CQ77" t="s">
         <v>11</v>
       </c>
     </row>
@@ -3133,19 +3148,19 @@
       <c r="C78" t="s">
         <v>25</v>
       </c>
-      <c r="CH78" t="s">
-        <v>5</v>
-      </c>
-      <c r="CI78" t="s">
-        <v>6</v>
-      </c>
       <c r="CJ78" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="CK78" t="s">
-        <v>10</v>
-      </c>
-      <c r="CO78" t="s">
+        <v>6</v>
+      </c>
+      <c r="CL78" t="s">
+        <v>8</v>
+      </c>
+      <c r="CM78" t="s">
+        <v>10</v>
+      </c>
+      <c r="CQ78" t="s">
         <v>11</v>
       </c>
     </row>
@@ -3159,19 +3174,19 @@
       <c r="C79" t="s">
         <v>27</v>
       </c>
-      <c r="CI79" t="s">
-        <v>5</v>
-      </c>
-      <c r="CJ79" t="s">
-        <v>6</v>
-      </c>
       <c r="CK79" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="CL79" t="s">
-        <v>10</v>
-      </c>
-      <c r="CO79" t="s">
+        <v>6</v>
+      </c>
+      <c r="CM79" t="s">
+        <v>8</v>
+      </c>
+      <c r="CN79" t="s">
+        <v>10</v>
+      </c>
+      <c r="CQ79" t="s">
         <v>11</v>
       </c>
     </row>
@@ -3185,24 +3200,18 @@
       <c r="C80" t="s">
         <v>28</v>
       </c>
-      <c r="CJ80" t="s">
-        <v>5</v>
-      </c>
-      <c r="CK80" t="s">
-        <v>6</v>
-      </c>
       <c r="CL80" t="s">
+        <v>5</v>
+      </c>
+      <c r="CM80" t="s">
+        <v>6</v>
+      </c>
+      <c r="CN80" t="s">
         <v>26</v>
       </c>
-      <c r="CM80" t="s">
+      <c r="CO80" t="s">
         <v>26</v>
       </c>
-      <c r="CN80" t="s">
-        <v>8</v>
-      </c>
-      <c r="CO80" t="s">
-        <v>8</v>
-      </c>
       <c r="CP80" t="s">
         <v>8</v>
       </c>
@@ -3210,6 +3219,12 @@
         <v>8</v>
       </c>
       <c r="CR80" t="s">
+        <v>8</v>
+      </c>
+      <c r="CS80" t="s">
+        <v>8</v>
+      </c>
+      <c r="CT80" t="s">
         <v>11</v>
       </c>
     </row>
@@ -3223,25 +3238,25 @@
       <c r="C81" t="s">
         <v>29</v>
       </c>
-      <c r="CK81" t="s">
-        <v>5</v>
-      </c>
-      <c r="CL81" t="s">
-        <v>6</v>
-      </c>
       <c r="CM81" t="s">
+        <v>5</v>
+      </c>
+      <c r="CN81" t="s">
+        <v>6</v>
+      </c>
+      <c r="CO81" t="s">
         <v>21</v>
       </c>
-      <c r="CR81" t="s">
-        <v>8</v>
-      </c>
-      <c r="CS81" t="s">
-        <v>8</v>
-      </c>
       <c r="CT81" t="s">
         <v>8</v>
       </c>
       <c r="CU81" t="s">
+        <v>8</v>
+      </c>
+      <c r="CV81" t="s">
+        <v>8</v>
+      </c>
+      <c r="CW81" t="s">
         <v>11</v>
       </c>
     </row>
@@ -3255,19 +3270,19 @@
       <c r="C82" t="s">
         <v>30</v>
       </c>
-      <c r="CL82" t="s">
-        <v>5</v>
-      </c>
-      <c r="CM82" t="s">
-        <v>6</v>
-      </c>
       <c r="CN82" t="s">
+        <v>5</v>
+      </c>
+      <c r="CO82" t="s">
+        <v>6</v>
+      </c>
+      <c r="CP82" t="s">
         <v>21</v>
       </c>
-      <c r="CU82" t="s">
-        <v>8</v>
-      </c>
-      <c r="CV82" t="s">
+      <c r="CW82" t="s">
+        <v>8</v>
+      </c>
+      <c r="CX82" t="s">
         <v>11</v>
       </c>
     </row>
@@ -3281,19 +3296,19 @@
       <c r="C83" t="s">
         <v>31</v>
       </c>
-      <c r="CM83" t="s">
-        <v>5</v>
-      </c>
-      <c r="CN83" t="s">
-        <v>6</v>
-      </c>
       <c r="CO83" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="CP83" t="s">
-        <v>10</v>
-      </c>
-      <c r="CV83" t="s">
+        <v>6</v>
+      </c>
+      <c r="CQ83" t="s">
+        <v>8</v>
+      </c>
+      <c r="CR83" t="s">
+        <v>10</v>
+      </c>
+      <c r="CX83" t="s">
         <v>11</v>
       </c>
     </row>
@@ -3307,19 +3322,19 @@
       <c r="C84" t="s">
         <v>32</v>
       </c>
-      <c r="CN84" t="s">
-        <v>5</v>
-      </c>
-      <c r="CO84" t="s">
-        <v>6</v>
-      </c>
       <c r="CP84" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="CQ84" t="s">
-        <v>10</v>
-      </c>
-      <c r="CV84" t="s">
+        <v>6</v>
+      </c>
+      <c r="CR84" t="s">
+        <v>8</v>
+      </c>
+      <c r="CS84" t="s">
+        <v>10</v>
+      </c>
+      <c r="CX84" t="s">
         <v>11</v>
       </c>
     </row>
@@ -3333,19 +3348,19 @@
       <c r="C85" t="s">
         <v>27</v>
       </c>
-      <c r="CO85" t="s">
-        <v>5</v>
-      </c>
-      <c r="CP85" t="s">
-        <v>6</v>
-      </c>
       <c r="CQ85" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="CR85" t="s">
-        <v>10</v>
-      </c>
-      <c r="CV85" t="s">
+        <v>6</v>
+      </c>
+      <c r="CS85" t="s">
+        <v>8</v>
+      </c>
+      <c r="CT85" t="s">
+        <v>10</v>
+      </c>
+      <c r="CX85" t="s">
         <v>11</v>
       </c>
     </row>
@@ -3359,17 +3374,11 @@
       <c r="C86" t="s">
         <v>28</v>
       </c>
-      <c r="CP86" t="s">
-        <v>5</v>
-      </c>
-      <c r="CQ86" t="s">
-        <v>6</v>
-      </c>
       <c r="CR86" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="CS86" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="CT86" t="s">
         <v>8</v>
@@ -3378,9 +3387,15 @@
         <v>8</v>
       </c>
       <c r="CV86" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="CW86" t="s">
+        <v>8</v>
+      </c>
+      <c r="CX86" t="s">
+        <v>10</v>
+      </c>
+      <c r="CY86" t="s">
         <v>11</v>
       </c>
     </row>
@@ -3394,25 +3409,25 @@
       <c r="C87" t="s">
         <v>29</v>
       </c>
-      <c r="CQ87" t="s">
-        <v>5</v>
-      </c>
-      <c r="CR87" t="s">
-        <v>6</v>
-      </c>
       <c r="CS87" t="s">
+        <v>5</v>
+      </c>
+      <c r="CT87" t="s">
+        <v>6</v>
+      </c>
+      <c r="CU87" t="s">
         <v>21</v>
       </c>
-      <c r="CV87" t="s">
-        <v>8</v>
-      </c>
-      <c r="CW87" t="s">
-        <v>8</v>
-      </c>
       <c r="CX87" t="s">
         <v>8</v>
       </c>
       <c r="CY87" t="s">
+        <v>8</v>
+      </c>
+      <c r="CZ87" t="s">
+        <v>8</v>
+      </c>
+      <c r="DA87" t="s">
         <v>11</v>
       </c>
     </row>
@@ -3426,19 +3441,19 @@
       <c r="C88" t="s">
         <v>30</v>
       </c>
-      <c r="CR88" t="s">
-        <v>5</v>
-      </c>
-      <c r="CS88" t="s">
-        <v>6</v>
-      </c>
       <c r="CT88" t="s">
+        <v>5</v>
+      </c>
+      <c r="CU88" t="s">
+        <v>6</v>
+      </c>
+      <c r="CV88" t="s">
         <v>21</v>
       </c>
-      <c r="CY88" t="s">
-        <v>8</v>
-      </c>
-      <c r="CZ88" t="s">
+      <c r="DA88" t="s">
+        <v>8</v>
+      </c>
+      <c r="DB88" t="s">
         <v>11</v>
       </c>
     </row>
@@ -3452,19 +3467,19 @@
       <c r="C89" t="s">
         <v>31</v>
       </c>
-      <c r="CS89" t="s">
-        <v>5</v>
-      </c>
-      <c r="CT89" t="s">
-        <v>6</v>
-      </c>
       <c r="CU89" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="CV89" t="s">
-        <v>10</v>
-      </c>
-      <c r="CZ89" t="s">
+        <v>6</v>
+      </c>
+      <c r="CW89" t="s">
+        <v>8</v>
+      </c>
+      <c r="CX89" t="s">
+        <v>10</v>
+      </c>
+      <c r="DB89" t="s">
         <v>11</v>
       </c>
     </row>
@@ -3478,19 +3493,19 @@
       <c r="C90" t="s">
         <v>32</v>
       </c>
-      <c r="CT90" t="s">
-        <v>5</v>
-      </c>
-      <c r="CU90" t="s">
-        <v>6</v>
-      </c>
       <c r="CV90" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="CW90" t="s">
-        <v>10</v>
-      </c>
-      <c r="CZ90" t="s">
+        <v>6</v>
+      </c>
+      <c r="CX90" t="s">
+        <v>8</v>
+      </c>
+      <c r="CY90" t="s">
+        <v>10</v>
+      </c>
+      <c r="DB90" t="s">
         <v>11</v>
       </c>
     </row>
@@ -3504,19 +3519,19 @@
       <c r="C91" t="s">
         <v>27</v>
       </c>
-      <c r="CU91" t="s">
-        <v>5</v>
-      </c>
-      <c r="CV91" t="s">
-        <v>6</v>
-      </c>
       <c r="CW91" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="CX91" t="s">
-        <v>10</v>
+        <v>6</v>
+      </c>
+      <c r="CY91" t="s">
+        <v>8</v>
       </c>
       <c r="CZ91" t="s">
+        <v>10</v>
+      </c>
+      <c r="DB91" t="s">
         <v>11</v>
       </c>
     </row>
@@ -3530,17 +3545,11 @@
       <c r="C92" t="s">
         <v>28</v>
       </c>
-      <c r="CV92" t="s">
-        <v>5</v>
-      </c>
-      <c r="CW92" t="s">
-        <v>6</v>
-      </c>
       <c r="CX92" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="CY92" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="CZ92" t="s">
         <v>8</v>
@@ -3549,6 +3558,12 @@
         <v>8</v>
       </c>
       <c r="DB92" t="s">
+        <v>8</v>
+      </c>
+      <c r="DC92" t="s">
+        <v>8</v>
+      </c>
+      <c r="DD92" t="s">
         <v>11</v>
       </c>
     </row>
@@ -3562,25 +3577,25 @@
       <c r="C93" t="s">
         <v>29</v>
       </c>
-      <c r="CW93" t="s">
-        <v>5</v>
-      </c>
-      <c r="CX93" t="s">
-        <v>6</v>
-      </c>
       <c r="CY93" t="s">
+        <v>5</v>
+      </c>
+      <c r="CZ93" t="s">
+        <v>6</v>
+      </c>
+      <c r="DA93" t="s">
         <v>21</v>
       </c>
-      <c r="DB93" t="s">
-        <v>8</v>
-      </c>
-      <c r="DC93" t="s">
-        <v>8</v>
-      </c>
       <c r="DD93" t="s">
         <v>8</v>
       </c>
       <c r="DE93" t="s">
+        <v>8</v>
+      </c>
+      <c r="DF93" t="s">
+        <v>8</v>
+      </c>
+      <c r="DG93" t="s">
         <v>11</v>
       </c>
     </row>
@@ -3594,19 +3609,19 @@
       <c r="C94" t="s">
         <v>30</v>
       </c>
-      <c r="CX94" t="s">
-        <v>5</v>
-      </c>
-      <c r="CY94" t="s">
-        <v>6</v>
-      </c>
       <c r="CZ94" t="s">
+        <v>5</v>
+      </c>
+      <c r="DA94" t="s">
+        <v>6</v>
+      </c>
+      <c r="DB94" t="s">
         <v>21</v>
       </c>
-      <c r="DE94" t="s">
-        <v>8</v>
-      </c>
-      <c r="DF94" t="s">
+      <c r="DG94" t="s">
+        <v>8</v>
+      </c>
+      <c r="DH94" t="s">
         <v>11</v>
       </c>
     </row>
@@ -3620,19 +3635,19 @@
       <c r="C95" t="s">
         <v>31</v>
       </c>
-      <c r="CY95" t="s">
-        <v>5</v>
-      </c>
-      <c r="CZ95" t="s">
-        <v>6</v>
-      </c>
       <c r="DA95" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="DB95" t="s">
-        <v>10</v>
-      </c>
-      <c r="DF95" t="s">
+        <v>6</v>
+      </c>
+      <c r="DC95" t="s">
+        <v>8</v>
+      </c>
+      <c r="DD95" t="s">
+        <v>10</v>
+      </c>
+      <c r="DH95" t="s">
         <v>11</v>
       </c>
     </row>
@@ -3646,19 +3661,19 @@
       <c r="C96" t="s">
         <v>32</v>
       </c>
-      <c r="CZ96" t="s">
-        <v>5</v>
-      </c>
-      <c r="DA96" t="s">
-        <v>6</v>
-      </c>
       <c r="DB96" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="DC96" t="s">
-        <v>10</v>
-      </c>
-      <c r="DF96" t="s">
+        <v>6</v>
+      </c>
+      <c r="DD96" t="s">
+        <v>8</v>
+      </c>
+      <c r="DE96" t="s">
+        <v>10</v>
+      </c>
+      <c r="DH96" t="s">
         <v>11</v>
       </c>
     </row>
@@ -3672,22 +3687,22 @@
       <c r="C97" t="s">
         <v>33</v>
       </c>
-      <c r="DC97" t="s">
-        <v>5</v>
-      </c>
-      <c r="DD97" t="s">
-        <v>6</v>
-      </c>
       <c r="DE97" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="DF97" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="DG97" t="s">
         <v>8</v>
       </c>
       <c r="DH97" t="s">
+        <v>8</v>
+      </c>
+      <c r="DI97" t="s">
+        <v>8</v>
+      </c>
+      <c r="DJ97" t="s">
         <v>11</v>
       </c>
     </row>
@@ -3701,25 +3716,25 @@
       <c r="C98" t="s">
         <v>34</v>
       </c>
-      <c r="DD98" t="s">
-        <v>5</v>
-      </c>
-      <c r="DE98" t="s">
-        <v>6</v>
-      </c>
       <c r="DF98" t="s">
+        <v>5</v>
+      </c>
+      <c r="DG98" t="s">
+        <v>6</v>
+      </c>
+      <c r="DH98" t="s">
         <v>21</v>
       </c>
-      <c r="DH98" t="s">
-        <v>8</v>
-      </c>
-      <c r="DI98" t="s">
-        <v>8</v>
-      </c>
       <c r="DJ98" t="s">
         <v>8</v>
       </c>
       <c r="DK98" t="s">
+        <v>8</v>
+      </c>
+      <c r="DL98" t="s">
+        <v>8</v>
+      </c>
+      <c r="DM98" t="s">
         <v>11</v>
       </c>
     </row>
@@ -3733,19 +3748,19 @@
       <c r="C99" t="s">
         <v>35</v>
       </c>
-      <c r="DE99" t="s">
-        <v>5</v>
-      </c>
-      <c r="DF99" t="s">
-        <v>6</v>
-      </c>
       <c r="DG99" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="DH99" t="s">
-        <v>10</v>
-      </c>
-      <c r="DK99" t="s">
+        <v>6</v>
+      </c>
+      <c r="DI99" t="s">
+        <v>8</v>
+      </c>
+      <c r="DJ99" t="s">
+        <v>10</v>
+      </c>
+      <c r="DM99" t="s">
         <v>11</v>
       </c>
     </row>
@@ -3759,16 +3774,19 @@
       <c r="C100" t="s">
         <v>36</v>
       </c>
-      <c r="DF100" t="s">
-        <v>5</v>
-      </c>
       <c r="DH100" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="DI100" t="s">
-        <v>10</v>
+        <v>6</v>
+      </c>
+      <c r="DJ100" t="s">
+        <v>8</v>
       </c>
       <c r="DK100" t="s">
+        <v>10</v>
+      </c>
+      <c r="DM100" t="s">
         <v>11</v>
       </c>
     </row>
@@ -3782,19 +3800,16 @@
       <c r="C101" t="s">
         <v>37</v>
       </c>
-      <c r="DG101" t="s">
-        <v>5</v>
-      </c>
-      <c r="DH101" t="s">
-        <v>6</v>
-      </c>
-      <c r="DI101" t="s">
-        <v>8</v>
-      </c>
-      <c r="DJ101" t="s">
-        <v>10</v>
-      </c>
       <c r="DK101" t="s">
+        <v>5</v>
+      </c>
+      <c r="DL101" t="s">
+        <v>6</v>
+      </c>
+      <c r="DM101" t="s">
+        <v>8</v>
+      </c>
+      <c r="DN101" t="s">
         <v>11</v>
       </c>
     </row>
@@ -3808,19 +3823,16 @@
       <c r="C102" t="s">
         <v>38</v>
       </c>
-      <c r="DH102" t="s">
-        <v>5</v>
-      </c>
-      <c r="DI102" t="s">
-        <v>6</v>
-      </c>
-      <c r="DJ102" t="s">
-        <v>8</v>
-      </c>
-      <c r="DK102" t="s">
-        <v>10</v>
-      </c>
       <c r="DL102" t="s">
+        <v>5</v>
+      </c>
+      <c r="DM102" t="s">
+        <v>6</v>
+      </c>
+      <c r="DN102" t="s">
+        <v>8</v>
+      </c>
+      <c r="DO102" t="s">
         <v>11</v>
       </c>
     </row>
@@ -3834,16 +3846,16 @@
       <c r="C103" t="s">
         <v>39</v>
       </c>
-      <c r="DI103" t="s">
-        <v>5</v>
-      </c>
-      <c r="DJ103" t="s">
-        <v>6</v>
-      </c>
-      <c r="DK103" t="s">
-        <v>8</v>
-      </c>
-      <c r="DL103" t="s">
+      <c r="DM103" t="s">
+        <v>5</v>
+      </c>
+      <c r="DN103" t="s">
+        <v>6</v>
+      </c>
+      <c r="DO103" t="s">
+        <v>8</v>
+      </c>
+      <c r="DP103" t="s">
         <v>11</v>
       </c>
     </row>
@@ -3857,16 +3869,16 @@
       <c r="C104" t="s">
         <v>40</v>
       </c>
-      <c r="DJ104" t="s">
-        <v>5</v>
-      </c>
-      <c r="DK104" t="s">
-        <v>6</v>
-      </c>
-      <c r="DL104" t="s">
-        <v>8</v>
-      </c>
-      <c r="DM104" t="s">
+      <c r="DN104" t="s">
+        <v>5</v>
+      </c>
+      <c r="DO104" t="s">
+        <v>6</v>
+      </c>
+      <c r="DP104" t="s">
+        <v>8</v>
+      </c>
+      <c r="DQ104" t="s">
         <v>11</v>
       </c>
     </row>
@@ -3880,16 +3892,16 @@
       <c r="C105" t="s">
         <v>41</v>
       </c>
-      <c r="DK105" t="s">
-        <v>5</v>
-      </c>
-      <c r="DL105" t="s">
-        <v>6</v>
-      </c>
-      <c r="DM105" t="s">
-        <v>8</v>
-      </c>
-      <c r="DN105" t="s">
+      <c r="DO105" t="s">
+        <v>5</v>
+      </c>
+      <c r="DP105" t="s">
+        <v>6</v>
+      </c>
+      <c r="DQ105" t="s">
+        <v>8</v>
+      </c>
+      <c r="DR105" t="s">
         <v>11</v>
       </c>
     </row>
@@ -3903,16 +3915,16 @@
       <c r="C106" t="s">
         <v>42</v>
       </c>
-      <c r="DL106" t="s">
-        <v>5</v>
-      </c>
-      <c r="DM106" t="s">
-        <v>6</v>
-      </c>
-      <c r="DN106" t="s">
-        <v>8</v>
-      </c>
-      <c r="DO106" t="s">
+      <c r="DP106" t="s">
+        <v>5</v>
+      </c>
+      <c r="DQ106" t="s">
+        <v>6</v>
+      </c>
+      <c r="DR106" t="s">
+        <v>8</v>
+      </c>
+      <c r="DS106" t="s">
         <v>11</v>
       </c>
     </row>
@@ -3926,16 +3938,16 @@
       <c r="C107" t="s">
         <v>43</v>
       </c>
-      <c r="DM107" t="s">
-        <v>5</v>
-      </c>
-      <c r="DN107" t="s">
-        <v>6</v>
-      </c>
-      <c r="DO107" t="s">
-        <v>8</v>
-      </c>
-      <c r="DP107" t="s">
+      <c r="DQ107" t="s">
+        <v>5</v>
+      </c>
+      <c r="DR107" t="s">
+        <v>6</v>
+      </c>
+      <c r="DS107" t="s">
+        <v>8</v>
+      </c>
+      <c r="DT107" t="s">
         <v>11</v>
       </c>
     </row>
@@ -3949,16 +3961,16 @@
       <c r="C108" t="s">
         <v>44</v>
       </c>
-      <c r="DN108" t="s">
-        <v>5</v>
-      </c>
-      <c r="DO108" t="s">
-        <v>6</v>
-      </c>
-      <c r="DP108" t="s">
-        <v>8</v>
-      </c>
-      <c r="DQ108" t="s">
+      <c r="DR108" t="s">
+        <v>5</v>
+      </c>
+      <c r="DS108" t="s">
+        <v>6</v>
+      </c>
+      <c r="DT108" t="s">
+        <v>8</v>
+      </c>
+      <c r="DU108" t="s">
         <v>11</v>
       </c>
     </row>
@@ -3972,16 +3984,16 @@
       <c r="C109" t="s">
         <v>45</v>
       </c>
-      <c r="DO109" t="s">
-        <v>5</v>
-      </c>
-      <c r="DP109" t="s">
-        <v>6</v>
-      </c>
-      <c r="DQ109" t="s">
-        <v>8</v>
-      </c>
-      <c r="DR109" t="s">
+      <c r="DS109" t="s">
+        <v>5</v>
+      </c>
+      <c r="DT109" t="s">
+        <v>6</v>
+      </c>
+      <c r="DU109" t="s">
+        <v>8</v>
+      </c>
+      <c r="DV109" t="s">
         <v>11</v>
       </c>
     </row>
